--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 3" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,6 +12,10 @@
     <sheet name="HYSTERECTOMIE KO 1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="EVENTRATION SEIN 1" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="AMYGDALITES ENFANT 1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ACCOUCHEMENT 3" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LV 1 COELIOSCOPIE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LV 2 COELIOSCOPIE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="CESARIENNE 6" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2442,12 +2446,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>00517</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>AIG. SUT. REVERDIN PAROI         220 MM TR CBE</t>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2461,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>01217</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>ALENE REDON COURBE CH 16 DIAM 5,3 MM</t>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
         </is>
       </c>
     </row>
@@ -2472,12 +2476,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>01217</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>ALENE REDON COURBE CH 16 DIAM 5,3 MM</t>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
         </is>
       </c>
     </row>
@@ -2487,12 +2491,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>02003</t>
+          <t>N060</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>BISTOURI MANCHE N 4 POUR LAMES FIG 18-19-20-21-22-23-24-25-36</t>
+          <t>PINCE PANSEM. FOERSTER STRIE 180 MM DTE</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2506,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>02602</t>
+          <t>UN140</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
+          <t>UP-NEEDLE MAYO HEGAR            200 MM       1/0 A 4/0</t>
         </is>
       </c>
     </row>
@@ -2517,12 +2521,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>02602</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2536,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>UN130</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>CROCHET GILLIES            190 MM PTU FORT</t>
+          <t>UP-NEEDLE MAYO HEGAR            180 MM       1/0 A 4/0</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2551,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>UC4312</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>CROCHET GILLIES            190 MM PTU FORT</t>
+          <t>CISEAUX UP-CUT MAYO        140 MM CBE</t>
         </is>
       </c>
     </row>
@@ -2562,12 +2566,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>UC4314</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>CROCHET GILLIES            190 MM PTU FORT</t>
+          <t>CISEAUX UP-CUT MAYO        170 MM CBE</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2581,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>UC4306</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>CROCHET GILLIES            190 MM PTU FORT</t>
+          <t>CISEAUX UP-CUT METZENBAUM 200 MM CBE</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2596,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>38305</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+          <t>PINCE PREHENS. AJOURE BABCOCK  160 MM TUNGST.</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2611,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>UC4309</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+          <t>CISEAUX UP-CUT METZENBAUM 250 MM CBE</t>
         </is>
       </c>
     </row>
@@ -2622,12 +2626,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>37705</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>ECARTEUR DBL HARTMANN RENFORCE  160 MM (PAIRE)</t>
+          <t>PINCE PANSEM. GROSS MAIER    250 MM DRT</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2641,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>35103</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ECARTEUR DBL HARTMANN RENFORCE  160 MM (PAIRE)</t>
+          <t>PINCE HEM. KELLY           160 MM C.SG</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2656,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>ECARTEUR DBL RICHARDSON EASTMANN (PAIRE)</t>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2671,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>ECARTEUR DBL RICHARDSON EASTMANN (PAIRE)</t>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2686,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>ECARTEUR ABDOM. RICARD VLV MEDIANE   70 X   50 MM</t>
+          <t>PINCE HEM. KOCHER          150 MM D.AG</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2701,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>35101</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>PASSE FILS OSHAUGN.FIN  200 MM CDE 90°</t>
+          <t>PINCE HEM. KELLY           140 MM C.SG</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2716,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>35101</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+          <t>PINCE HEM. KELLY           140 MM C.SG</t>
         </is>
       </c>
     </row>
@@ -2727,12 +2731,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>38902</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  150 MM   5 X  6</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2746,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2761,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>02602</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2776,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>UC4313</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+          <t>CISEAUX UP-CUT MAYO        170 MM DRT</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2791,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>UN120</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>PINCE DISS.  DEBAKEY 2.0   200 MM DRT ATRAUMA</t>
+          <t>UP-NEEDLE MAYO HEGAR            160 MM       1/0 A 4/0</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2806,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>PINCE DISS.  STAND. DELIC. 180 MM A  GR</t>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2821,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>34203</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>PINCE DISS.  STAND. DELIC. 180 MM SS GR</t>
+          <t>PINCE HEM. BENGOLEA        210 MM C.SG</t>
         </is>
       </c>
     </row>
@@ -2847,12 +2851,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>34203</t>
+          <t>38902</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. BENGOLEA        210 MM C.SG</t>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  150 MM   5 X  6</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2866,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KELLY           140 MM C.SG</t>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2881,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KELLY           140 MM C.SG</t>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
         </is>
       </c>
     </row>
@@ -2922,12 +2926,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>35103</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KELLY           160 MM C.SG</t>
+          <t>PASSE FILS OSHAUGN.FIN  200 MM CDE 90°</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2941,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>35403</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KOCHER          150 MM D.AG</t>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2986,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>02602</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
         </is>
       </c>
     </row>
@@ -2997,12 +3001,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>01217</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+          <t>ALENE REDON COURBE CH 16 DIAM 5,3 MM</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3016,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>02003</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+          <t>BISTOURI MANCHE N 4 POUR LAMES FIG 18-19-20-21-22-23-24-25-36</t>
         </is>
       </c>
     </row>
@@ -3027,12 +3031,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>30910</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+          <t>PINCE DISS.  STAND. DELIC. 180 MM SS GR</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3046,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>30909</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+          <t>PINCE DISS.  STAND. DELIC. 180 MM A  GR</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3061,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>37609</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+          <t>PINCE DISS.  DEBAKEY 2.0   200 MM DRT ATRAUMA</t>
         </is>
       </c>
     </row>
@@ -3072,12 +3076,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>37609</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3091,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>37609</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3106,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>PINCE PANSEM. GROSS MAIER    250 MM DRT</t>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3121,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>PINCE PREHENS. AJOURE BABCOCK  160 MM TUNGST.</t>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3136,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>PINCE PREHENS. MULTIGR. ALLIS  150 MM   5 X  6</t>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3151,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>00517</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>PINCE PREHENS. MULTIGR. ALLIS  150 MM   5 X  6</t>
+          <t>AIG. SUT. REVERDIN PAROI         220 MM TR CBE</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3166,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3181,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3196,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
+          <t>CROCHET GILLIES            190 MM PTU FORT</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3211,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>47207</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>VALVE DOYEN VAGINALE             35 X   90 MM</t>
+          <t>CROCHET GILLIES            190 MM PTU FORT</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3226,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>52919</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>VALVE KELLY   260 MM             50 X 38 MM</t>
+          <t>CROCHET GILLIES            190 MM PTU FORT</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3241,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>K1007</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>CUPULE INOX  D.   80 MM CAPACITE 225CC</t>
+          <t>CROCHET GILLIES            190 MM PTU FORT</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3256,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>K1008</t>
+          <t>01217</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+          <t>ALENE REDON COURBE CH 16 DIAM 5,3 MM</t>
         </is>
       </c>
     </row>
@@ -3267,12 +3271,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>N060</t>
+          <t>47207</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>PINCE PANSEM. FOERSTER STRIE 180 MM DTE</t>
+          <t>VALVE DOYEN VAGINALE             35 X   90 MM</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3286,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>UC4306</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>CISEAUX UP-CUT METZENBAUM 200 MM CBE</t>
+          <t>ECARTEUR DBL RICHARDSON EASTMANN (PAIRE)</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3301,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>UC4309</t>
+          <t>W792</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>CISEAUX UP-CUT METZENBAUM 250 MM CBE</t>
+          <t>ECARTEUR /MANCHE KELLY              65 X 50 MM 260 MM</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3316,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>UC4312</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>CISEAUX UP-CUT MAYO        140 MM CBE</t>
+          <t>ECARTEUR DBL RICHARDSON EASTMANN (PAIRE)</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3331,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>UC4313</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>CISEAUX UP-CUT MAYO        170 MM DRT</t>
+          <t>ECARTEUR ABDOM. RICARD VLV MEDIANE   70 X   50 MM</t>
         </is>
       </c>
     </row>
@@ -3342,12 +3346,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>UC4314</t>
+          <t>52919</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>CISEAUX UP-CUT MAYO        170 MM CBE</t>
+          <t>VALVE KELLY   260 MM             50 X 38 MM</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3361,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>UN120</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>UP-NEEDLE MAYO HEGAR            160 MM       1/0 A 4/0</t>
+          <t>ECARTEUR DBL HARTMANN RENFORCE  160 MM (PAIRE)</t>
         </is>
       </c>
     </row>
@@ -3372,12 +3376,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>UN130</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>UP-NEEDLE MAYO HEGAR            180 MM       1/0 A 4/0</t>
+          <t>ECARTEUR DBL HARTMANN RENFORCE  160 MM (PAIRE)</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3391,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>UN140</t>
+          <t>K1007</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>UP-NEEDLE MAYO HEGAR            200 MM       1/0 A 4/0</t>
+          <t>CUPULE INOX  D.   80 MM CAPACITE 225CC</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3406,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>W792</t>
+          <t>K1008</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>ECARTEUR /MANCHE KELLY              65 X 50 MM 260 MM</t>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3467,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>02728</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>CANULE ASPIR. YANKAUER          260 MM D. 9 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3482,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>02728</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>CANULE ASPIR. YANKAUER          260 MM D. 9 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
         </is>
       </c>
     </row>
@@ -3493,12 +3497,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET. LARGEUR INTERIEURE 10 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 15MM</t>
         </is>
       </c>
     </row>
@@ -3523,12 +3527,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET. LARGEUR INTERIEURE 10 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3542,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET. LARGEUR INTERIEURE 10 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
         </is>
       </c>
     </row>
@@ -3553,12 +3557,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 10 MM</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3572,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 19 MM</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3587,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 10 MM</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3632,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 18MM</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3647,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3677,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3692,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 19 MM</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3707,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
         </is>
       </c>
     </row>
@@ -3718,12 +3722,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3737,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 15MM</t>
         </is>
       </c>
     </row>
@@ -3748,12 +3752,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 15MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
         </is>
       </c>
     </row>
@@ -3778,12 +3782,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 15MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 10 MM</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3797,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 15MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3812,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 18MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3827,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 18MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3842,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 18MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 19 MM</t>
         </is>
       </c>
     </row>
@@ -3853,12 +3857,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 10 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
         </is>
       </c>
     </row>
@@ -3868,12 +3872,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 10 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
         </is>
       </c>
     </row>
@@ -3883,12 +3887,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 10 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 18MM</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3902,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 10 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
         </is>
       </c>
     </row>
@@ -3928,12 +3932,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3947,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 15MM</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3962,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 11 MM</t>
         </is>
       </c>
     </row>
@@ -3973,12 +3977,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET. LARGEUR INTERIEURE 10 MM</t>
         </is>
       </c>
     </row>
@@ -3988,12 +3992,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET. LARGEUR INTERIEURE 10 MM</t>
         </is>
       </c>
     </row>
@@ -4003,12 +4007,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 18MM</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4022,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET. LARGEUR INTERIEURE 10 MM</t>
         </is>
       </c>
     </row>
@@ -4033,12 +4037,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
         </is>
       </c>
     </row>
@@ -4048,12 +4052,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 10 MM</t>
         </is>
       </c>
     </row>
@@ -4063,12 +4067,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 16 MM</t>
+          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 13 MM</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4082,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>02728</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 19 MM</t>
+          <t>CANULE ASPIR. YANKAUER          260 MM D. 9 MM</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4097,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 19 MM</t>
+          <t>COUTEAU O.R.L. BECKMANN AMYGD. VEGET.  LARGEUR INTERIEURE 13MM</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4112,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>02728</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>COUTEAU O.R.L. MOURE   A  PANIER 220 X 19 MM</t>
+          <t>CANULE ASPIR. YANKAUER          260 MM D. 9 MM</t>
         </is>
       </c>
     </row>
@@ -4123,12 +4127,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>OUVRE BOUCHE DOYEN ADULTE 150 MM AV 2 PROT.SILICONE</t>
+          <t>PINCE DIVERS MAGILL INTUBATION ENFANT  200 MM</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4142,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>31706</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>OUVRE BOUCHE DOYEN ENFANT 120 MM AV 2 PROT.SILICONE</t>
+          <t>PINCE DIVERS MAGILL INTUBATION NOURR.  170 MM</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4157,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>Z523</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>OUVRE BOUCHE JENNINGS                    80 MM</t>
+          <t>PINCE ORL AMYGDALES HARTMANN     7 MM X 140 MM</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4172,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>OUVRE BOUCHE JENNINGS                    80 MM</t>
+          <t>OUVRE BOUCHE JENNINGS                  110 MM</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4187,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>26105</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>OUVRE BOUCHE JENNINGS                  110 MM</t>
+          <t>OUVRE BOUCHE JENNINGS                  150 MM</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4217,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>26105</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>OUVRE BOUCHE JENNINGS                  110 MM</t>
+          <t>OUVRE BOUCHE JENNINGS                    80 MM</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4262,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>OUVRE BOUCHE JENNINGS                  130 MM</t>
+          <t>OUVRE BOUCHE JENNINGS                  110 MM</t>
         </is>
       </c>
     </row>
@@ -4273,12 +4277,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>OUVRE BOUCHE JENNINGS                  150 MM</t>
+          <t>OUVRE BOUCHE JENNINGS                  130 MM</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4292,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>PINCE DIVERS MAGILL INTUBATION ENFANT  200 MM</t>
+          <t>OUVRE BOUCHE JENNINGS                    80 MM</t>
         </is>
       </c>
     </row>
@@ -4303,12 +4307,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>31706</t>
+          <t>26102</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>PINCE DIVERS MAGILL INTUBATION NOURR.  170 MM</t>
+          <t>OUVRE BOUCHE DOYEN ADULTE 150 MM AV 2 PROT.SILICONE</t>
         </is>
       </c>
     </row>
@@ -4318,12 +4322,1861 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Z523</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>PINCE ORL AMYGDALES HARTMANN     7 MM X 140 MM</t>
+          <t>OUVRE BOUCHE DOYEN ENFANT 120 MM AV 2 PROT.SILICONE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ACCOUCHEMENT 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>VALVE DOYEN VAGINALE             45 X   90 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>30914</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. DELIC. 250 MM SS GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>UC4314</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT MAYO        170 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>03207</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX COURANTS  MSS     160 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>UN140</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            200 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>35409</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          240 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>37609</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>36006</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. ROCHESTER PEAN 200 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>35409</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          240 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>35407</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          210 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>37607</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIE 250 MM DTE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LV 1 COELIOSCOPIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>K1008</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>45504</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM GYNECO COLLIN            32 X 105 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>25501</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>HYSTEROMETRE SIMS    MALLEABLE                  330 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>03612</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX COURANTS MAYO LEXER  165 MM CBE TUNGST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>02802</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>CANULE BIOPSIE NOVAK   END.UTER. 230 MM D. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>50619</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>BISTOURI MANCHE DOUBLE N 3/4 POUR LAMES FIG 10A 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>30909</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. DELIC. 180 MM A  GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>30929</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. NORMA. 160 MM SS GR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>02602</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. LONGUETTE   300 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>35303</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM C.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>35303</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM C.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>04117</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX DISS. METZ.NELSON 200 MM CBE  TUNGST</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>37609</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>UN120</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            160 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>2430013</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>0483</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>14058</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>1900002</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>1900113</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>140164</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LV 2 COELIOSCOPIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>2390000</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>1900113</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>14058</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>18009M2</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>2430013</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>17240829 0011</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>17240829 008</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>17240829 043</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>17240829 047</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>6230901</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>16240731 024</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>16240731</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>17231011 002</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>140164</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>17230324 017</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>K1008</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>02602</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>30924</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. NORMA. 145 MM 1 X 2 GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>30929</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. NORMA. 160 MM SS GR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>37801</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. LONGUETTE   240 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>02001</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>BISTOURI MANCHE N 3 POUR LAMES FIG 10-11-12-12d-13-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>03510</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX COURANTS MAYO        170 MM CBE TUNGST</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>35303</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM C.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>35303</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          150 MM C.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>37609</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>35203</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KELLY RANKIN    160 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>UN120</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            160 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>UC4306</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM 200 MM CBE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CESARIENNE 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>02003</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>BISTOURI MANCHE N 4 POUR LAMES FIG 18-19-20-21-22-23-24-25-36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>30909</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. DELIC. 180 MM A  GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>30912</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. DELIC. 200 MM SS GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>47210</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>VALVE DOYEN VAGINALE             45 X 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>21603</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR ABDOM. ROCHARD       VLV SUSP.100 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>K1008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>45506</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM GYNECO COLLIN            38 X 105 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>02602</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>37705</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. GROSS MAIER    250 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>UC4324</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM DELICAT 180 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>UC4312</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT MAYO        140 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>34203</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. BENGOLEA        210 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>35103</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KELLY           160 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>33603</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>PINCE GYNECO JL FAURE ART.UTERINE FORTE 200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>33603</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>PINCE GYNECO JL FAURE ART.UTERINE FORTE 200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>38403</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. AJOURE COEUR    200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>38401</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. AJOURE COEUR    160 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>38403</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. AJOURE COEUR    200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>37607</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIE 250 MM DTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>UN130</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            180 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>UN140</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            200 MM       1/0 A 4/0</t>
         </is>
       </c>
     </row>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -16,6 +16,7 @@
     <sheet name="LV 1 COELIOSCOPIE" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="LV 2 COELIOSCOPIE" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="CESARIENNE 6" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CESARIENNE 2" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -900,6 +901,502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CESARIENNE 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>K1008</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>45505</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM GYNECO COLLIN            35 X 105 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>21604</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR ABDOM. ROCHARD       VLV SUSP.120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>30933</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. NORMA. 200 MM 1 X 2 GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>30935</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. NORMA. 200 MM SS GR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>47213</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>VALVE DOYEN VAGINALE             60 X 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 140 MM L.P10X25 L.P15X30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>02003</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>BISTOURI MANCHE N 4 POUR LAMES FIG 18-19-20-21-22-23-24-25-36</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>37705</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. GROSS MAIER    250 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>38403</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. AJOURE COEUR    200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>38401</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. AJOURE COEUR    160 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>38403</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. AJOURE COEUR    200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>37609</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>33603</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>PINCE GYNECO JL FAURE ART.UTERINE FORTE 200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>33603</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>PINCE GYNECO JL FAURE ART.UTERINE FORTE 200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>35203</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KELLY RANKIN    160 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>35103</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KELLY           160 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>UN140</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            200 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>UN130</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            180 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>UC4314</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT MAYO        170 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>03612</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX COURANTS MAYO LEXER  165 MM CBE TUNGST</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>02602</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="12" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="13" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 3" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="HERNIER APPENDICITE 3" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="HERNIE APPENDICITE 3" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="HERNIE APPENDICITE 4" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="HERNIE APPENDICITE 1" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <si>
     <t xml:space="preserve">CESARIENNE 3</t>
   </si>
@@ -908,6 +909,27 @@
   </si>
   <si>
     <t xml:space="preserve">PINCE PREHENS. MULTIGR. ALLIS  150 MM   4 X  5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HERNIE APPENDICITE 1</t>
+  </si>
+  <si>
+    <t>30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  DEBAKEY 2.7   160 MM DRT ATRAUMA</t>
+  </si>
+  <si>
+    <t>51143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. LOWER V. BIL.   180 MM   CBE</t>
+  </si>
+  <si>
+    <t>UC4311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT MAYO        140 MM DRT</t>
   </si>
 </sst>
 </file>
@@ -3069,6 +3091,486 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
@@ -3078,7 +3580,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3">
@@ -3097,10 +3599,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5">
@@ -3117,10 +3619,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>264</v>
+        <v>54</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>265</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -3139,10 +3641,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -3150,10 +3652,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -3161,10 +3663,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>283</v>
+        <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>284</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -3172,10 +3674,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -3183,10 +3685,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>266</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>13</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13">
@@ -3238,10 +3740,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>286</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -3249,10 +3751,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -3260,10 +3762,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20">
@@ -3271,10 +3773,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>4</v>
+        <v>214</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>5</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21">
@@ -3282,10 +3784,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>289</v>
+        <v>28</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>290</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -3293,10 +3795,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -3304,10 +3806,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24">
@@ -3315,10 +3817,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25">
@@ -3326,10 +3828,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26">
@@ -3337,10 +3839,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27">
@@ -3348,10 +3850,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28">
@@ -3359,10 +3861,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29">
@@ -3370,10 +3872,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30">
@@ -3381,10 +3883,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31">
@@ -3392,10 +3894,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>291</v>
+        <v>119</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>292</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32">
@@ -3403,10 +3905,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33">
@@ -3414,10 +3916,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -3425,10 +3927,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
@@ -3436,10 +3938,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>123</v>
+        <v>291</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36">
@@ -3447,10 +3949,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>123</v>
+        <v>291</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37">
@@ -3458,10 +3960,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38">
@@ -3469,10 +3971,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39">
@@ -3480,10 +3982,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -3491,10 +3993,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>123</v>
+        <v>289</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>124</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41">
@@ -3502,10 +4004,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42">
@@ -3513,10 +4015,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43">
@@ -3524,10 +4026,21 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>37</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -6094,14 +6607,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>192</v>
       </c>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -23,6 +23,7 @@
     <sheet name="HERNIE APPENDICITE 1" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="GOITRE 2" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="GOITRE 1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="DCN 1" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5296,6 +5297,472 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DCN 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>46010</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM ORL RHINO. KILLIAN        50 X 130 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>46011</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM ORL RHINO. KILLIAN        35 X 130 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>46008</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM ORL RHINO. KILLIAN        75 X 130 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>55604</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>DISSECTEUR FREER ASPIRATEUR 210 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>N544</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>MAILLET HAJEK                             215 MM               140 GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>46005</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM ORL RHINO. HARTMANN HALL  30 X 150 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>17301</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>DISSECTEUR LERICHE            170 MM X 3.5 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>17307</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>DISSECTEUR SACHS             210 X 3 MM TRANCHANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>56615</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>PINCE ORL OTOLOGIE PANS.      180 MM STRIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>07415</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>CIS. OS GOUGE  KILLIAN BAION.EN V         5 X 160 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>29601</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  ADSON BROWN   120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>02001</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>BISTOURI MANCHE N 3 POUR LAMES FIG 10-11-12-12d-13-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>52307</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE NEURO RAY HORIZ. 4MM 90°</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>UC4382</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM 145 MM CBE ERGONOMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>17805</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL SENN MILLER        GR. MSS 160 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>C8YZ</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR /MANCHE FOMON BOUTONNE    160 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>02705</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>CANULE ASPIR. FRAZIER CDEE      180 MM  D.  3,3 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>37904</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. PEAN        160 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>A5KZ</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX NEURO OLIVECRONA        230 MM TRIJUMEAU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>02704</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>CANULE ASPIR. FRAZIER CDEE      180 MM  D.  2,6 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>UC4312</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT MAYO        140 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>02807</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>CANULE HEPARINE  D. 2.5 MM EMB.4 MM FIG 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>UC4335</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT IRIS        115 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>NU53</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>A7ZQ</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>PINCE ORL RHINO LUC MRS FENETRE A DGT MOYENNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>K1006</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D.   60 MM CAPACITE 75CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>K1007</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D.   80 MM CAPACITE 225CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>K1008</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -24,6 +24,7 @@
     <sheet name="GOITRE 2" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="GOITRE 1" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="DCN 1" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="KYSTE HYDATIQUE DU FOIE 1" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5763,6 +5764,922 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KYSTE HYDATIQUE DU FOIE 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>47506</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>VALVE LERICHE BUGATTI            45 X 260 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>02004</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>BISTOURI MANCHE N 4 LONG POUR LAMES FIG 18-19-20-21-22-23-24-25-36</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>02002</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>BISTOURI MANCHE N 3 LONG POUR LAMES FIG 10-11-12-12d-13-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>52929</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR MALLEABLE HABERER 37/45 X 300 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>30914</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. DELIC. 250 MM SS GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>30935</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. NORMA. 200 MM SS GR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>30007</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  DEBAKEY 3.5   240 MM DRT ATRAUMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>30909</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  STAND. DELIC. 180 MM A  GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>17810</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL US ARMY 15 X 33 ET 16 X 46 210 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>02728</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>CANULE ASPIR. YANKAUER          260 MM D. 9 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>N867</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR ABDOM. BALFOUR OUV.200 LT.100 M.100X70</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>47213</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>VALVE DOYEN VAGINALE             60 X 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>47210</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>VALVE DOYEN VAGINALE             45 X 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>17809</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>58011</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>TROCART OSCHNER VESICULE CH 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>N867</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR ABDOM. BALFOUR OUV.200 LT.100 M.100X70</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>35405</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KOCHER          180 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>34203</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. BENGOLEA        210 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>35101</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KELLY           140 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>35103</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KELLY           160 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>35513</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. LERICHE         150 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>37705</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. GROSS MAIER    250 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>35513</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. LERICHE         150 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>26712</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>PASSE FILS OSHAUGN.FIN  240 MM CDE 90°</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>26710</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>PASSE FILS OSHAUGN.FIN  220 MM CDE 90°</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>35513</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. LERICHE         150 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>34203</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. BENGOLEA        210 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>38902</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  150 MM   5 X  6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>35103</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. KELLY           160 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>34203</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. BENGOLEA        210 MM C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>38903</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>38903</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>34202</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. BENGOLEA        210 MM D.AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>38903</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  190 MM    5 X 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>37607</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIE 250 MM DTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>37607</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIE 250 MM DTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>37609</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>37609</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIEE 200 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>UC4308</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM 230 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>UC4308</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM 230 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>UC4304</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM 180 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>UC4306</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM 200 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>UN140</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            200 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>UN145</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            240 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>UN130</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE MAYO HEGAR            180 MM       1/0 A 4/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>28402</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>PINCE CHAMPS BACKAUS 120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>52206</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>HARICOT INOX 200 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>K1008</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>K1301</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX D. 150 MM CAPACITE 900CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>02602</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -25,6 +25,7 @@
     <sheet name="GOITRE 1" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="DCN 1" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="KYSTE HYDATIQUE DU FOIE 1" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="MINI FRAG 2" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6680,6 +6681,888 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MINI FRAG 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>17504</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 120 MM L.P  8X20 L.P10X25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>17504</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 120 MM L.P  8X20 L.P10X25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>17504</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 120 MM L.P  8X20 L.P10X25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>17504</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL FARABEUF (PAIRE) 120 MM L.P  8X20 L.P10X25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>33305</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>PINCE GOUGE SIMPLE LUER FRIEDMANN 140 X 2 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>32502</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>PINCE GOUGE DBL ART. BOHLER     150 X  2MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>29304</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>PINCE COUPANTE SIMPLE LISTON    170 MM COUDEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Z590</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>DAVIER OS VERBRUGGE REDUCT. AUTO CENTR.  150 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Z590</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>DAVIER OS VERBRUGGE REDUCT. AUTO CENTR.  150 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>15813</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE OSS. VOLKMANN              170 X   2 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>15817</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE OSS. VOLKMANN              170 X   4 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>17205</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>DISSECTEUR KILLIAN              190 MM MSS/TRANCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>18504</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR /MANCHE HOHMANN 160 MM   6.0 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>18502</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR /MANCHE HOHMANN 150 MM   5.0 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>18506</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR /MANCHE HOHMANN 160 MM   8.0 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>02001</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>BISTOURI MANCHE N 3 POUR LAMES FIG 10-11-12-12d-13-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>CROCHET GILLIES            190 MM PTU FORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>CROCHET GILLIES            190 MM PTU FIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>18502</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR /MANCHE HOHMANN 150 MM   5.0 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>45103</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>SONDE CANNELEE                                    140 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>21901</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR AUT.ALM  4 X 4 GR. MSS          70 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>22502</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR AUT.JANSEN GR 4X4 MSS   20 X 100 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>22801</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR AUT.WEITLANER GR. MSS 2 X 3  105 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>29304</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>PINCE COUPANTE SIMPLE LISTON    170 MM COUDEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>29601</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  ADSON BROWN   120 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>29517</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  ADSON  120 X 1,5 MM A  GR.TUNGST</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>30304</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  GERALD       180 X 1,5 MM A  GR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>30401</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>PINCE DISS.  GILLIES         150 MM A  GR.UPLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>22205</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR AUT.FINSEN  GR. MSS 2 X 3     50 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>K1306</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>CIS. OS OSTEOT. COTTLE                             9 X 180 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>K1307</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>CIS. OS OSTEOT. COTTLE                             6 X 180 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>N785</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>CIS. OS OSTEOT. COTTLE                             4 X 180 MM GRADUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>N785</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>CIS. OS OSTEOT. COTTLE                             4 X 180 MM GRADUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>17204</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>DISSECTEUR HURD                  225 MM AMYGDALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>17204</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>DISSECTEUR HURD                  225 MM AMYGDALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>17805</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL SENN MILLER        GR. MSS 160 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>17805</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>ECARTEUR DBL SENN MILLER        GR. MSS 160 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>K1007</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D.   80 MM CAPACITE 225CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>K1006</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D.   60 MM CAPACITE 75CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>37904</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. PEAN        160 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>UN430</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>UP-NEEDLE CRILE WOOD              150 MM       4/0 A 6/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>NU53</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>02602</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>CADRE EPINGLE PORTE PINCES  150 MM A BOULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>03408</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX COURANTS IRIDECTOMIE 115 MM CBE TUNGST</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>UC4311</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT MAYO        140 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>UC4302</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM 145 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>UC4302</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>CISEAUX UP-CUT METZENBAUM 145 MM CBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>38901</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PREHENS. MULTIGR. ALLIS  150 MM   4 X  5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>16408</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>DAVIER OS REDUCTEUR PETITS OS                        135 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>34912</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. HALSTEAD         120 MM MICRO D.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>34910</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. HALSTEAD         120 MM MICRO C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>34910</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. HALSTEAD         120 MM MICRO C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>34910</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>PINCE HEM. HALSTEAD         120 MM MICRO C.SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>26702</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>PASSE FILS OSHAUGN.FIN  120 MM CDE 90°</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>26702</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>PASSE FILS OSHAUGN.FIN  120 MM CDE 90°</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -26,6 +26,8 @@
     <sheet name="DCN 1" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="KYSTE HYDATIQUE DU FOIE 1" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="MINI FRAG 2" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="CURETAGE 3" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="CURETAGE 4" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8074,6 +8076,623 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CURETAGE 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>K1008</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>45505</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM GYNECO COLLIN            35 X 105 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>K1230</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>VALVE AUVARD            83 X 38 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>14817</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE GYNECO GOURDET MOUSSE      260 X 10 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>14815</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE GYNECO GOURDET MOUSSE      260 X   6 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>37607</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIE 250 MM DTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>37705</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. GROSS MAIER    250 MM DRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>14816</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE GYNECO GOURDET MOUSSE      260 X   8 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>14814</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE GYNECO GOURDET MOUSSE      260 X   4 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>27503</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>PINCE BIOPSIE GYNECO DOUAY                                250 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>25514</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>HYSTEROMETRE SIMS   RIGIDE                330 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CURETAGE 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Réf</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>K1008</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>CUPULE INOX  D. 100 MM CAPACITE 325CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>02149</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>BOUGIE HEGAR DOUBLE SERIE EN BOITE N° 3-4 A 17-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>K1230</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>VALVE AUVARD            83 X 38 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>45506</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>SPECULUM GYNECO COLLIN            38 X 105 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>37607</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. FOERSTER STRIE 250 MM DTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>37804</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>PINCE PANSEM. LONGUETTE   240 MM CDE CHERON</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>33801</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>PINCE GYNECO POZZI            240 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>14815</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE GYNECO GOURDET MOUSSE      260 X   6 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>14816</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE GYNECO GOURDET MOUSSE      260 X   8 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>14816</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>CURETTE GYNECO GOURDET MOUSSE      260 X   8 MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>25501</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>HYSTEROMETRE SIMS    MALLEABLE                  330 MM</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="26"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="27" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 3" sheetId="1" state="visible" r:id="rId1"/>
@@ -34,13 +34,17 @@
     <sheet name="RHINOPLASTIE 1" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="CERCLAGE 4" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="ORTHOPEDIE MS 1" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="ABDOMEN ENFANT 1" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="634">
   <si>
     <t xml:space="preserve">CESARIENNE 3</t>
   </si>
@@ -1900,6 +1904,48 @@
   </si>
   <si>
     <t xml:space="preserve">PASSE FILS OSHAUGN.FIN  140 MM CDE 45°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABDOMEN ENFANT 1</t>
+  </si>
+  <si>
+    <t>47202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVE DEAVER                     25 X 200 MM</t>
+  </si>
+  <si>
+    <t>30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  DEBAKEY 3.5   200 MM DRT ATRAUMA</t>
+  </si>
+  <si>
+    <t>56011</t>
+  </si>
+  <si>
+    <t>17506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR DBL FARABEUF CORTY (PAIRE) 200 MM L.P30X40 L.P40X55</t>
+  </si>
+  <si>
+    <t>20904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR ABDOM. GOSSET SS CREM. 30 X 35 X 150</t>
+  </si>
+  <si>
+    <t>34302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. BENGOLEA        240 MM FINE     C.SG UPLINE</t>
+  </si>
+  <si>
+    <t>34906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. HALSTEAD         120 MM C.SG</t>
   </si>
 </sst>
 </file>
@@ -2482,14 +2528,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2863,14 +2909,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>258</v>
       </c>
@@ -3233,14 +3279,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>263</v>
       </c>
@@ -3724,14 +3770,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>287</v>
       </c>
@@ -4237,14 +4283,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>294</v>
       </c>
@@ -4651,14 +4697,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>297</v>
       </c>
@@ -5131,14 +5177,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>302</v>
       </c>
@@ -5699,14 +5745,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>346</v>
       </c>
@@ -6223,14 +6269,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>356</v>
       </c>
@@ -6571,14 +6617,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>400</v>
       </c>
@@ -7249,14 +7295,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>418</v>
       </c>
@@ -7903,14 +7949,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -8284,14 +8330,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>475</v>
       </c>
@@ -8533,14 +8579,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>490</v>
       </c>
@@ -8749,14 +8795,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>493</v>
       </c>
@@ -8998,14 +9044,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>514</v>
       </c>
@@ -9258,14 +9304,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>517</v>
       </c>
@@ -9408,14 +9454,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>518</v>
       </c>
@@ -9910,14 +9956,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>560</v>
       </c>
@@ -10069,13 +10115,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="65.8515625"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -10859,7 +10905,597 @@
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="63.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -10870,14 +11506,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -11603,14 +12239,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>112</v>
       </c>
@@ -12358,14 +12994,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>155</v>
       </c>
@@ -13036,14 +13672,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>192</v>
       </c>
@@ -13208,14 +13844,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>203</v>
       </c>
@@ -13589,14 +14225,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>231</v>
       </c>
@@ -14025,14 +14661,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>251</v>
       </c>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="32"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -38,16 +38,15 @@
     <sheet name="ABDOMEN ENFANT 1" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="PROCTO 1" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="PROCTO 2" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ARTRO 1" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="ARTRO 2" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="658">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -1988,6 +1987,39 @@
   </si>
   <si>
     <t xml:space="preserve">SONDE CANNELEE MODELE COURBE 140 MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTRO 1</t>
+  </si>
+  <si>
+    <t>31175RE.2RE</t>
+  </si>
+  <si>
+    <t>36124</t>
+  </si>
+  <si>
+    <t>39712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTE AIG. DEBAKEY                 230 MM TUNGST</t>
+  </si>
+  <si>
+    <t>S3431XA.SL</t>
+  </si>
+  <si>
+    <t>S3431XB.UL</t>
+  </si>
+  <si>
+    <t>S3431XC.UM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTRO 2</t>
+  </si>
+  <si>
+    <t>S3431XB</t>
+  </si>
+  <si>
+    <t>S3431XB.UR</t>
   </si>
 </sst>
 </file>
@@ -2570,14 +2602,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2940,14 +2972,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>226</v>
       </c>
@@ -3321,14 +3353,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>252</v>
       </c>
@@ -3757,14 +3789,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>270</v>
       </c>
@@ -4248,14 +4280,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>290</v>
       </c>
@@ -4761,14 +4793,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>297</v>
       </c>
@@ -5175,14 +5207,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>300</v>
       </c>
@@ -5655,14 +5687,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>305</v>
       </c>
@@ -6223,14 +6255,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>349</v>
       </c>
@@ -6747,14 +6779,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>359</v>
       </c>
@@ -7095,14 +7127,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>403</v>
       </c>
@@ -7773,14 +7805,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -8154,14 +8186,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>421</v>
       </c>
@@ -8808,14 +8840,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>478</v>
       </c>
@@ -9057,14 +9089,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>493</v>
       </c>
@@ -9273,14 +9305,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>496</v>
       </c>
@@ -9522,14 +9554,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>517</v>
       </c>
@@ -9782,14 +9814,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>520</v>
       </c>
@@ -9932,14 +9964,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>521</v>
       </c>
@@ -10434,14 +10466,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>563</v>
       </c>
@@ -10595,14 +10627,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>566</v>
       </c>
@@ -11988,7 +12020,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="66.421875"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -12369,7 +12401,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="65.28125"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -12706,7 +12738,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="65.57421875"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -13040,6 +13072,460 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -13054,7 +13540,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="65.28125"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -13442,14 +13928,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
@@ -14175,14 +14661,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>130</v>
       </c>
@@ -14930,14 +15416,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>171</v>
       </c>
@@ -15652,14 +16138,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>178</v>
       </c>
@@ -16330,14 +16816,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>215</v>
       </c>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="32"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="33"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -40,13 +40,14 @@
     <sheet name="PROCTO 2" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="ARTRO 1" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="ARTRO 2" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="COLPOSCOPIE CONSULTATION GYNECO" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="659">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -2020,6 +2021,9 @@
   </si>
   <si>
     <t>S3431XB.UR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLPOSCOPIE CONSULTATION GYNECO</t>
   </si>
 </sst>
 </file>
@@ -13080,7 +13084,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
@@ -13287,12 +13291,250 @@
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
@@ -13307,7 +13549,7 @@
   <sheetData>
     <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3">
@@ -13326,10 +13568,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
@@ -13337,10 +13579,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -13348,10 +13590,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
@@ -13359,10 +13601,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
@@ -13370,10 +13612,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>509</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">
@@ -13381,10 +13623,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -13392,131 +13634,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="33"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="28"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -35,19 +35,20 @@
     <sheet name="RHINOPLASTIE 1" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="CERCLAGE 4" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="ORTHOPEDIE MS 1" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="ABDOMEN ENFANT 1" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="PROCTO 1" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="PROCTO 2" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="ARTRO 1" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="ARTRO 2" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="COLPOSCOPIE CONSULTATION GYNECO" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="ORTHOPEDIE RACHIS LAMBAIRE 1" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="ABDOMEN ENFANT 1" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="PROCTO 1" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="PROCTO 2" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="ARTRO 1" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="ARTRO 2" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="COLPOSCOPIE CONSULTATION GYNECO" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="746">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -1918,6 +1919,279 @@
     <t xml:space="preserve">DAVIER OS VERBRUGGE REDUCT. AUTO CENTR.  240 MM</t>
   </si>
   <si>
+    <t xml:space="preserve">ORTHOPEDIE RACHIS LAMBAIRE 1</t>
+  </si>
+  <si>
+    <t>01215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALENE REDON COURBE CH 14 DIAM 4,6 MM</t>
+  </si>
+  <si>
+    <t>02723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANULE ASPIR. WERTHEIMER RIG.CD 170 MM D. 3 MM</t>
+  </si>
+  <si>
+    <t>14001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROCHET CUSHING         190 MM FIN  MSSE 4 MM</t>
+  </si>
+  <si>
+    <t>14003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROCHET CUSHING         190 MM FORT MSSE 6 MM</t>
+  </si>
+  <si>
+    <t>14006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROCHET DANDY            230 MM MSSE DROIT</t>
+  </si>
+  <si>
+    <t>15720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. CLOWARD DROITE           200 X  4.8 MM FIG 3</t>
+  </si>
+  <si>
+    <t>17105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISSECTEUR DAVIS 245 MM UN COTE TRANCHANT 6 MM UN COTE MOUSSE  6,8 MM </t>
+  </si>
+  <si>
+    <t>17201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISSECTEUR FREER 200 MM  1 COTE MOUSSE 5MM 1 COTE TRANCHANT 4,5 MM</t>
+  </si>
+  <si>
+    <t>19002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE LOVE        COUDE 45° 190 MM</t>
+  </si>
+  <si>
+    <t>19003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE LOVE        COUDE 90° 190 MM</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>21807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.ADSON BECKMANN 320 MM MSS 25X38</t>
+  </si>
+  <si>
+    <t>21910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.BECKMANN      MSS    50X 300 MM</t>
+  </si>
+  <si>
+    <t>22009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.BECKMANN STILLE MSS     35X 330 MM</t>
+  </si>
+  <si>
+    <t>22803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.WEITLANER GR. MSS 3 X 4  130 MM</t>
+  </si>
+  <si>
+    <t>23606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. SCOV. HAVERFIELD  150 MM SEUL</t>
+  </si>
+  <si>
+    <t>29007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE COUPANTE DBL ART. LISTON KEY HORSLEY 260 MM          </t>
+  </si>
+  <si>
+    <t>32603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE DBL ART. LEKSELL    230 X  8MM</t>
+  </si>
+  <si>
+    <t>32902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE DBL ART. SMITH PETERSEN 230 MM CBE</t>
+  </si>
+  <si>
+    <t>34302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. BENGOLEA        240 MM FINE     C.SG UPLINE</t>
+  </si>
+  <si>
+    <t>39712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTE AIG. DEBAKEY                 230 MM TUNGST</t>
+  </si>
+  <si>
+    <t>41901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 CDE BAS 2X10</t>
+  </si>
+  <si>
+    <t>41902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 CDE HT  2X10</t>
+  </si>
+  <si>
+    <t>41903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 DROIT   2X10</t>
+  </si>
+  <si>
+    <t>41904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 CDE BAS 3X10</t>
+  </si>
+  <si>
+    <t>41905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 CDE HT  3X10</t>
+  </si>
+  <si>
+    <t>41906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 DROIT   3X10</t>
+  </si>
+  <si>
+    <t>41907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 CDE BAS 4X10</t>
+  </si>
+  <si>
+    <t>41908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 CDE HT  4X10</t>
+  </si>
+  <si>
+    <t>41912C</t>
+  </si>
+  <si>
+    <t>42106C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE SPURLING CERAM.180 CDE HT  4X10</t>
+  </si>
+  <si>
+    <t>42305C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA CERAM.PM 180 X 1 MM 40° HT  DEM.</t>
+  </si>
+  <si>
+    <t>42308C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA CERAM.PM 180 X 2 MM 40° HT  DEM.</t>
+  </si>
+  <si>
+    <t>42313C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA CERAM.PM 180 X 3 MM 40° HT  DEM.</t>
+  </si>
+  <si>
+    <t>42319C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA CERAM.PM 200 X 5 MM 90° HT  DEM.</t>
+  </si>
+  <si>
+    <t>42331C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA CERAM.PM 200 X 4 MM 40° HT  DEM.</t>
+  </si>
+  <si>
+    <t>43013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGINE COBB RACHIS MCHE ROND   240 X 19 MM</t>
+  </si>
+  <si>
+    <t>43309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGINE LAMBOTTE                   25 X 210 MM</t>
+  </si>
+  <si>
+    <t>54307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAILLET WILLIGER 26X240MM 300g REMPL PLOMB</t>
+  </si>
+  <si>
+    <t>K632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. LAMBOTTE             8 X 240 MM LAME FINE</t>
+  </si>
+  <si>
+    <t>UC4306C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT METZENBAUM 200 MM CBE CERAM</t>
+  </si>
+  <si>
+    <t>UC4308C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT METZENBAUM 230 MM CBE CERAM</t>
+  </si>
+  <si>
+    <t>UC4332C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT MAYO STILLE 170 MM CBE CERAM</t>
+  </si>
+  <si>
+    <t>W467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE KOCHER 230 MM 60 X 25 MM</t>
+  </si>
+  <si>
+    <t>W544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. LAMBOTTE           10 X 240 MM COURBE</t>
+  </si>
+  <si>
+    <t>W811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. COBB                  280 X   8.5 MM</t>
+  </si>
+  <si>
     <t xml:space="preserve">ABDOMEN ENFANT 1</t>
   </si>
   <si>
@@ -1939,12 +2213,6 @@
     <t xml:space="preserve">PINCE DISS.  DEBAKEY 3.5   200 MM DRT ATRAUMA</t>
   </si>
   <si>
-    <t>34302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE HEM. BENGOLEA        240 MM FINE     C.SG UPLINE</t>
-  </si>
-  <si>
     <t>34906</t>
   </si>
   <si>
@@ -1997,12 +2265,6 @@
   </si>
   <si>
     <t>36124</t>
-  </si>
-  <si>
-    <t>39712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTE AIG. DEBAKEY                 230 MM TUNGST</t>
   </si>
   <si>
     <t>S3431XA.SL</t>
@@ -11428,13 +11690,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="60"/>
+    <col customWidth="1" min="3" max="3" width="76.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -11458,10 +11720,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>76</v>
+        <v>624</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>77</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5">
@@ -11469,10 +11731,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>78</v>
+        <v>404</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>79</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6">
@@ -11480,10 +11742,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>436</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>437</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -11491,10 +11753,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>436</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>437</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -11502,10 +11764,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>626</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>11</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9">
@@ -11513,10 +11775,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>628</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>11</v>
+        <v>629</v>
       </c>
     </row>
     <row r="10">
@@ -11524,10 +11786,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11">
@@ -11535,10 +11797,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
     </row>
     <row r="12">
@@ -11546,10 +11808,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>137</v>
+        <v>634</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>138</v>
+        <v>635</v>
       </c>
     </row>
     <row r="13">
@@ -11557,10 +11819,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>137</v>
+        <v>636</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>138</v>
+        <v>637</v>
       </c>
     </row>
     <row r="14">
@@ -11568,10 +11830,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>271</v>
+        <v>638</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>232</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15">
@@ -11579,10 +11841,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>272</v>
+        <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -11590,10 +11852,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>626</v>
+        <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -11601,10 +11863,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>599</v>
+        <v>640</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>600</v>
+        <v>641</v>
       </c>
     </row>
     <row r="18">
@@ -11612,10 +11874,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>298</v>
+        <v>642</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>299</v>
+        <v>643</v>
       </c>
     </row>
     <row r="19">
@@ -11623,10 +11885,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>14</v>
+        <v>644</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>15</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20">
@@ -11634,10 +11896,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>14</v>
+        <v>406</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>15</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
@@ -11645,10 +11907,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>14</v>
+        <v>645</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>15</v>
+        <v>646</v>
       </c>
     </row>
     <row r="22">
@@ -11656,10 +11918,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>14</v>
+        <v>647</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>15</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23">
@@ -11667,10 +11929,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>14</v>
+        <v>649</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>15</v>
+        <v>650</v>
       </c>
     </row>
     <row r="24">
@@ -11678,10 +11940,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>143</v>
+        <v>651</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>144</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25">
@@ -11689,10 +11951,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
     </row>
     <row r="26">
@@ -11700,10 +11962,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -11711,10 +11973,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>295</v>
+        <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>296</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -11722,10 +11984,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -11733,10 +11995,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -11744,10 +12006,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>630</v>
+        <v>14</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>631</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -11755,10 +12017,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>632</v>
+        <v>655</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>633</v>
+        <v>656</v>
       </c>
     </row>
     <row r="32">
@@ -11766,10 +12028,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>464</v>
+        <v>301</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>465</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33">
@@ -11777,10 +12039,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>148</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34">
@@ -11788,10 +12050,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35">
@@ -11799,10 +12061,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>147</v>
+        <v>657</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>148</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36">
@@ -11810,10 +12072,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>22</v>
+        <v>659</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>23</v>
+        <v>660</v>
       </c>
     </row>
     <row r="37">
@@ -11821,10 +12083,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>661</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>25</v>
+        <v>662</v>
       </c>
     </row>
     <row r="38">
@@ -11832,10 +12094,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>150</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
@@ -11843,10 +12105,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
@@ -11854,10 +12116,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>26</v>
+        <v>663</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>27</v>
+        <v>664</v>
       </c>
     </row>
     <row r="41">
@@ -11865,10 +12127,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>222</v>
+        <v>665</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>223</v>
+        <v>666</v>
       </c>
     </row>
     <row r="42">
@@ -11876,10 +12138,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>330</v>
+        <v>667</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>331</v>
+        <v>668</v>
       </c>
     </row>
     <row r="43">
@@ -11887,10 +12149,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>34</v>
+        <v>669</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>35</v>
+        <v>670</v>
       </c>
     </row>
     <row r="44">
@@ -11898,10 +12160,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
     </row>
     <row r="45">
@@ -11909,10 +12171,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>114</v>
+        <v>671</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>115</v>
+        <v>672</v>
       </c>
     </row>
     <row r="46">
@@ -11920,10 +12182,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>250</v>
+        <v>673</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>251</v>
+        <v>674</v>
       </c>
     </row>
     <row r="47">
@@ -11931,10 +12193,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>636</v>
+        <v>675</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>232</v>
+        <v>676</v>
       </c>
     </row>
     <row r="48">
@@ -11942,10 +12204,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>336</v>
+        <v>677</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>337</v>
+        <v>678</v>
       </c>
     </row>
     <row r="49">
@@ -11953,10 +12215,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>40</v>
+        <v>679</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>41</v>
+        <v>680</v>
       </c>
     </row>
     <row r="50">
@@ -11964,10 +12226,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>71</v>
+        <v>681</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>72</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51">
@@ -11975,10 +12237,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>341</v>
+        <v>682</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>342</v>
+        <v>683</v>
       </c>
     </row>
     <row r="52">
@@ -11986,10 +12248,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>44</v>
+        <v>684</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>45</v>
+        <v>685</v>
       </c>
     </row>
     <row r="53">
@@ -11997,10 +12259,252 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>474</v>
+        <v>686</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>475</v>
+        <v>687</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3">
+        <v>63</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3">
+        <v>64</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3">
+        <v>65</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3">
+        <v>66</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3">
+        <v>67</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3">
+        <v>68</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3">
+        <v>69</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3">
+        <v>70</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3">
+        <v>71</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3">
+        <v>72</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>713</v>
       </c>
     </row>
   </sheetData>
@@ -12008,8 +12512,8 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="91" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -12410,7 +12914,7 @@
   <sheetData>
     <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>714</v>
       </c>
     </row>
     <row r="3">
@@ -12429,10 +12933,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -12440,10 +12944,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -12451,10 +12955,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>436</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7">
@@ -12462,10 +12966,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>436</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8">
@@ -12473,10 +12977,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -12484,10 +12988,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>242</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>243</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -12495,10 +12999,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>715</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>716</v>
       </c>
     </row>
     <row r="11">
@@ -12506,10 +13010,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>715</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>148</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12">
@@ -12517,10 +13021,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -12528,10 +13032,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -12539,10 +13043,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>149</v>
+        <v>271</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15">
@@ -12550,10 +13054,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>174</v>
+        <v>272</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>175</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16">
@@ -12561,10 +13065,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>330</v>
+        <v>717</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>331</v>
+        <v>718</v>
       </c>
     </row>
     <row r="17">
@@ -12572,10 +13076,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>599</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>31</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -12583,10 +13087,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>32</v>
+        <v>298</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>33</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19">
@@ -12594,10 +13098,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -12605,10 +13109,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -12616,10 +13120,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>638</v>
+        <v>14</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>639</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -12627,10 +13131,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>640</v>
+        <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>641</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -12638,10 +13142,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>640</v>
+        <v>14</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>641</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -12649,10 +13153,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>353</v>
+        <v>143</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>354</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
@@ -12660,10 +13164,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>642</v>
+        <v>719</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>643</v>
+        <v>720</v>
       </c>
     </row>
     <row r="26">
@@ -12671,10 +13175,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>159</v>
+        <v>51</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>160</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
@@ -12682,10 +13186,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>40</v>
+        <v>295</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>41</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28">
@@ -12693,10 +13197,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>163</v>
+        <v>55</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -12704,10 +13208,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -12715,10 +13219,263 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
         <v>44</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="B47" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
         <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -12747,7 +13504,7 @@
   <sheetData>
     <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>644</v>
+        <v>726</v>
       </c>
     </row>
     <row r="3">
@@ -12843,10 +13600,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
@@ -12953,10 +13710,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>638</v>
+        <v>727</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>639</v>
+        <v>728</v>
       </c>
     </row>
     <row r="22">
@@ -12964,10 +13721,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>640</v>
+        <v>729</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>641</v>
+        <v>730</v>
       </c>
     </row>
     <row r="23">
@@ -12975,10 +13732,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>640</v>
+        <v>729</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>641</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24">
@@ -12997,10 +13754,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>642</v>
+        <v>731</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>643</v>
+        <v>732</v>
       </c>
     </row>
     <row r="26">
@@ -13030,10 +13787,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>645</v>
+        <v>163</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>646</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29">
@@ -13041,10 +13798,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>163</v>
+        <v>42</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -13052,20 +13809,9 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3">
-        <v>28</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="4" t="s">
         <v>45</v>
       </c>
     </row>
@@ -13095,7 +13841,7 @@
   <sheetData>
     <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>647</v>
+        <v>733</v>
       </c>
     </row>
     <row r="3">
@@ -13114,10 +13860,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -13125,10 +13871,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>229</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>230</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -13169,10 +13915,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -13180,10 +13926,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -13191,10 +13937,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -13202,10 +13948,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -13213,10 +13959,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>648</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14">
@@ -13224,10 +13970,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>649</v>
+        <v>149</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -13235,10 +13981,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>650</v>
+        <v>174</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>651</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -13246,10 +13992,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>652</v>
+        <v>330</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>232</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17">
@@ -13257,10 +14003,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>653</v>
+        <v>30</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>232</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -13268,10 +14014,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>653</v>
+        <v>32</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>232</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -13279,10 +14025,142 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>654</v>
+        <v>108</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>232</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -13311,7 +14189,7 @@
   <sheetData>
     <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>655</v>
+        <v>736</v>
       </c>
     </row>
     <row r="3">
@@ -13341,10 +14219,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6">
@@ -13396,10 +14274,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -13418,10 +14296,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>648</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>232</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -13429,7 +14307,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>649</v>
+        <v>737</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>232</v>
@@ -13440,7 +14318,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>649</v>
+        <v>738</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>232</v>
@@ -13451,10 +14329,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>663</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>31</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16">
@@ -13462,7 +14340,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>652</v>
+        <v>739</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>232</v>
@@ -13473,7 +14351,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>656</v>
+        <v>740</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>232</v>
@@ -13484,7 +14362,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>657</v>
+        <v>740</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>232</v>
@@ -13495,32 +14373,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>654</v>
+        <v>741</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -13538,7 +14394,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
@@ -13549,7 +14405,7 @@
   <sheetData>
     <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>658</v>
+        <v>742</v>
       </c>
     </row>
     <row r="3">
@@ -13568,10 +14424,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>241</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -13579,10 +14435,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -13590,10 +14446,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -13601,10 +14457,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -13612,10 +14468,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>509</v>
+        <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>510</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -13623,10 +14479,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -13634,10 +14490,131 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>35</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -13646,7 +14623,124 @@
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="36" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="40" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -35,15 +35,19 @@
     <sheet name="RHINOPLASTIE 1" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="CERCLAGE 4" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="ORTHOPEDIE MS 1" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="ORTHOPEDIE RACHIS LAMBAIRE 1" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="ABDOMEN ENFANT 1" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="PROCTO 1" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="PROCTO 2" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="ARTRO 1" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="ARTRO 2" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="COLPOSCOPIE CONSULTATION GYNECO" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="EMBROCHAGE OSTEO 1" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="AMPUTATION 1" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="ABDOMEN ENFANT 1" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="PROCTO 1" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="PROCTO 2" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ARTRO 1" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="ARTRO 2" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="COLPOSCOPIE CONSULTATION GYNECO" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="EMBROCHAGE OSTEO 1" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="AMPUTATION 1" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="ORTHOPEDIE RACHIS LOMBAIRE 1" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="ORTHOPEDIE RACHIS LOMBAIRE 2" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="ORTHOPEDIE RACHIS LOMBAIRE 2 (TEST)" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="ORTHOPEDIE RACHIS CERBICAL 1" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="ORTHOPEDIE RACHIS CERBICAL 2" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -53,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="897">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -1924,7 +1928,226 @@
     <t xml:space="preserve">DAVIER OS VERBRUGGE REDUCT. AUTO CENTR.  240 MM</t>
   </si>
   <si>
-    <t xml:space="preserve">ORTHOPEDIE RACHIS LAMBAIRE 1</t>
+    <t xml:space="preserve">ABDOMEN ENFANT 1</t>
+  </si>
+  <si>
+    <t>17506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR DBL FARABEUF CORTY (PAIRE) 200 MM L.P30X40 L.P40X55</t>
+  </si>
+  <si>
+    <t>20904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR ABDOM. GOSSET SS CREM. 30 X 35 X 150</t>
+  </si>
+  <si>
+    <t>30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  DEBAKEY 3.5   200 MM DRT ATRAUMA</t>
+  </si>
+  <si>
+    <t>34302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. BENGOLEA        240 MM FINE     C.SG UPLINE</t>
+  </si>
+  <si>
+    <t>34906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. HALSTEAD         120 MM C.SG</t>
+  </si>
+  <si>
+    <t>47202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVE DEAVER                     25 X 200 MM</t>
+  </si>
+  <si>
+    <t>56011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCTO 1</t>
+  </si>
+  <si>
+    <t>45101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONDE BOUTONNE FEUILLE MYRTE   140 MM</t>
+  </si>
+  <si>
+    <t>46201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STYLET BOUTONNE AVEC CHAS            140 MM</t>
+  </si>
+  <si>
+    <t>A4MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DILATATEUR RECTAL MATHIEU               195 MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCTO 2</t>
+  </si>
+  <si>
+    <t>N786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONDE CANNELEE MODELE COURBE 140 MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTRO 1</t>
+  </si>
+  <si>
+    <t>31175RE.2RE</t>
+  </si>
+  <si>
+    <t>36124</t>
+  </si>
+  <si>
+    <t>39712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTE AIG. DEBAKEY                 230 MM TUNGST</t>
+  </si>
+  <si>
+    <t>S3431XA.SL</t>
+  </si>
+  <si>
+    <t>S3431XB.UL</t>
+  </si>
+  <si>
+    <t>S3431XC.UM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTRO 2</t>
+  </si>
+  <si>
+    <t>S3431XB</t>
+  </si>
+  <si>
+    <t>S3431XB.UR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLPOSCOPIE CONSULTATION GYNECO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBROCHAGE OSTEO 1</t>
+  </si>
+  <si>
+    <t>25816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANDRIN INOX UNIVERSEL AV. CLE POIGNEE EN T Diam. max broche 5mm</t>
+  </si>
+  <si>
+    <t>32101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE FILS COUPE 150 D.MAX 1,5 MM DBL ARTIC.</t>
+  </si>
+  <si>
+    <t>32306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE FILS PREHENS. UNIV.          INOX 185 MM</t>
+  </si>
+  <si>
+    <t>54703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHE AO 145/120 3,2MM</t>
+  </si>
+  <si>
+    <t>54707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHE AO 100/75 DIAM 2MM</t>
+  </si>
+  <si>
+    <t>58323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANC. MECHE BROCH HELICO.LONGUE 2,5MM</t>
+  </si>
+  <si>
+    <t>K1026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANC. TOURNEVIS HEXAGONAL MANCHE CELERON 2.5 MM</t>
+  </si>
+  <si>
+    <t>K1027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANC. TOURNEVIS HEXAGONAL MANCHE CELERON 3.5 MM</t>
+  </si>
+  <si>
+    <t>K1073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANC. FORET INOX AO DIAM. 2.0 X 100 MM</t>
+  </si>
+  <si>
+    <t>K1075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANC. FORET INOX AO DIAM. 2.7 X 100 MM</t>
+  </si>
+  <si>
+    <t>Kirschner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPUTATION 1</t>
+  </si>
+  <si>
+    <t>19504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE SAUERBRUCH   20 X   72 225 MM</t>
+  </si>
+  <si>
+    <t>29709</t>
+  </si>
+  <si>
+    <t>33002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE DBL ART. ZAUFAL JANSEN 180 X 4 MM CBE</t>
+  </si>
+  <si>
+    <t>41504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPE PUTTI              240 MM X 13 MM</t>
+  </si>
+  <si>
+    <t>44804</t>
+  </si>
+  <si>
+    <t>C5YF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE DBL ART. MAYFIELD        180 X  3MM CBE</t>
+  </si>
+  <si>
+    <t>UC4334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT DUBOST          210 MM CBE</t>
+  </si>
+  <si>
+    <t>W467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE KOCHER 230 MM 60 X 25 MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORTHOPEDIE RACHIS LOMBAIRE 1</t>
   </si>
   <si>
     <t>01215</t>
@@ -2038,18 +2261,6 @@
     <t xml:space="preserve">PINCE GOUGE DBL ART. SMITH PETERSEN 230 MM CBE</t>
   </si>
   <si>
-    <t>34302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE HEM. BENGOLEA        240 MM FINE     C.SG UPLINE</t>
-  </si>
-  <si>
-    <t>39712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTE AIG. DEBAKEY                 230 MM TUNGST</t>
-  </si>
-  <si>
     <t>41901</t>
   </si>
   <si>
@@ -2179,12 +2390,6 @@
     <t xml:space="preserve">CISEAUX UP-CUT MAYO STILLE 170 MM CBE CERAM</t>
   </si>
   <si>
-    <t>W467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECARTEUR /MANCHE KOCHER 230 MM 60 X 25 MM</t>
-  </si>
-  <si>
     <t>W544</t>
   </si>
   <si>
@@ -2197,205 +2402,352 @@
     <t xml:space="preserve">CURETTE OSS. COBB                  280 X   8.5 MM</t>
   </si>
   <si>
-    <t xml:space="preserve">ABDOMEN ENFANT 1</t>
-  </si>
-  <si>
-    <t>17506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECARTEUR DBL FARABEUF CORTY (PAIRE) 200 MM L.P30X40 L.P40X55</t>
-  </si>
-  <si>
-    <t>20904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECARTEUR ABDOM. GOSSET SS CREM. 30 X 35 X 150</t>
-  </si>
-  <si>
-    <t>30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE DISS.  DEBAKEY 3.5   200 MM DRT ATRAUMA</t>
-  </si>
-  <si>
-    <t>34906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE HEM. HALSTEAD         120 MM C.SG</t>
-  </si>
-  <si>
-    <t>47202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVE DEAVER                     25 X 200 MM</t>
-  </si>
-  <si>
-    <t>56011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROCTO 1</t>
-  </si>
-  <si>
-    <t>45101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SONDE BOUTONNE FEUILLE MYRTE   140 MM</t>
-  </si>
-  <si>
-    <t>46201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STYLET BOUTONNE AVEC CHAS            140 MM</t>
-  </si>
-  <si>
-    <t>A4MP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DILATATEUR RECTAL MATHIEU               195 MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROCTO 2</t>
-  </si>
-  <si>
-    <t>N786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SONDE CANNELEE MODELE COURBE 140 MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARTRO 1</t>
-  </si>
-  <si>
-    <t>31175RE.2RE</t>
-  </si>
-  <si>
-    <t>36124</t>
-  </si>
-  <si>
-    <t>S3431XA.SL</t>
-  </si>
-  <si>
-    <t>S3431XB.UL</t>
-  </si>
-  <si>
-    <t>S3431XC.UM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARTRO 2</t>
-  </si>
-  <si>
-    <t>S3431XB</t>
-  </si>
-  <si>
-    <t>S3431XB.UR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLPOSCOPIE CONSULTATION GYNECO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMBROCHAGE OSTEO 1</t>
-  </si>
-  <si>
-    <t>25816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANDRIN INOX UNIVERSEL AV. CLE POIGNEE EN T Diam. max broche 5mm</t>
-  </si>
-  <si>
-    <t>32101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE FILS COUPE 150 D.MAX 1,5 MM DBL ARTIC.</t>
-  </si>
-  <si>
-    <t>32306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE FILS PREHENS. UNIV.          INOX 185 MM</t>
-  </si>
-  <si>
-    <t>54703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHE AO 145/120 3,2MM</t>
-  </si>
-  <si>
-    <t>54707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHE AO 100/75 DIAM 2MM</t>
-  </si>
-  <si>
-    <t>58323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANC. MECHE BROCH HELICO.LONGUE 2,5MM</t>
-  </si>
-  <si>
-    <t>K1026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANC. TOURNEVIS HEXAGONAL MANCHE CELERON 2.5 MM</t>
-  </si>
-  <si>
-    <t>K1027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANC. TOURNEVIS HEXAGONAL MANCHE CELERON 3.5 MM</t>
-  </si>
-  <si>
-    <t>K1073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANC. FORET INOX AO DIAM. 2.0 X 100 MM</t>
-  </si>
-  <si>
-    <t>K1075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANC. FORET INOX AO DIAM. 2.7 X 100 MM</t>
-  </si>
-  <si>
-    <t>Kirschner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPUTATION 1</t>
-  </si>
-  <si>
-    <t>19504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECARTEUR /MANCHE SAUERBRUCH   20 X   72 225 MM</t>
-  </si>
-  <si>
-    <t>29709</t>
-  </si>
-  <si>
-    <t>33002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE GOUGE DBL ART. ZAUFAL JANSEN 180 X 4 MM CBE</t>
-  </si>
-  <si>
-    <t>41504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAPE PUTTI              240 MM X 13 MM</t>
-  </si>
-  <si>
-    <t>44804</t>
-  </si>
-  <si>
-    <t>C5YF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE GOUGE DBL ART. MAYFIELD        180 X  3MM CBE</t>
-  </si>
-  <si>
-    <t>UC4334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISEAUX UP-CUT DUBOST          210 MM CBE</t>
+    <t xml:space="preserve">ORTHOPEDIE RACHIS LOMBAIRE 2</t>
+  </si>
+  <si>
+    <t>02702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANULE ASPIR. FRAZIER CDEE      125 MM  D.  3,3 MM</t>
+  </si>
+  <si>
+    <t>02703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANULE ASPIR. FRAZIER CDEE      125 MM  D.  4   MM</t>
+  </si>
+  <si>
+    <t>02725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANULE ASPIR. WERTHEIMER RIG.CD 170 MM D. 5 MM</t>
+  </si>
+  <si>
+    <t>08106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. LAMBOTTE             8 X 240 MM</t>
+  </si>
+  <si>
+    <t>15617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. BRUNS ANGULEE   230 X  4.8 MM FIG 3</t>
+  </si>
+  <si>
+    <t>25822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAILLET COLLIN          200 MM      220 GR</t>
+  </si>
+  <si>
+    <t>32506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE DBL ART. ECHLIN       230 X  3MM CDE</t>
+  </si>
+  <si>
+    <t>39713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTE AIG. DEBAKEY                 260 MM TUNGST</t>
+  </si>
+  <si>
+    <t>41909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 DROIT   4X10</t>
+  </si>
+  <si>
+    <t>42317C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA CERAM.PM 180 X 4 MM 40° HT  DEM.</t>
+  </si>
+  <si>
+    <t>42323C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA CERAM.PM 200 X 5 MM 40° HT  DEM.</t>
+  </si>
+  <si>
+    <t>42324C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA CERAM.PM 200 X 4 MM 90° HT  DEM.</t>
+  </si>
+  <si>
+    <t>43012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGINE COBB RACHIS MCHE ROND   240 X 13 MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORTHOPEDIE RACHIS LOMBAIRE 2 (TEST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORTHOPEDIE RACHIS CERBICAL 1</t>
+  </si>
+  <si>
+    <t>02722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANULE ASPIR. WERTHEIMER RIG.CD 170 MM D. 2 MM</t>
+  </si>
+  <si>
+    <t>02724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANULE ASPIR. WERTHEIMER RIG.CD 170 MM D. 4 MM</t>
+  </si>
+  <si>
+    <t>15304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE O.R.L. LEMPERT AURIC.      210 X  2.5</t>
+  </si>
+  <si>
+    <t>15605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. BRUNS DROITE    230 X  3.7 MM FIG 1</t>
+  </si>
+  <si>
+    <t>15613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. BRUNS ANGULEE   230 X  2.5 MM FIG 00</t>
+  </si>
+  <si>
+    <t>15811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. CLOWARD CTRE CDEE     200 X  2.8 MM</t>
+  </si>
+  <si>
+    <t>15812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. CLOWARD CTRE CDEE     200 X  3.3 MM</t>
+  </si>
+  <si>
+    <t>17210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREER YASARGIL ELEVATEUR A CLOISON</t>
+  </si>
+  <si>
+    <t>22203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.DOS D'ANE GR.MSS        170 MM</t>
+  </si>
+  <si>
+    <t>23103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE        40 MM</t>
+  </si>
+  <si>
+    <t>23105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE        45 MM</t>
+  </si>
+  <si>
+    <t>23106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE GR. 50 MM</t>
+  </si>
+  <si>
+    <t>23107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE        50 MM</t>
+  </si>
+  <si>
+    <t>23108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE GR. 55 MM</t>
+  </si>
+  <si>
+    <t>23109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE        55 MM</t>
+  </si>
+  <si>
+    <t>23110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE GR. 60 MM</t>
+  </si>
+  <si>
+    <t>23111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE        60 MM</t>
+  </si>
+  <si>
+    <t>29101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE COUPANTE DBL ART. LISTON RUSKIN 180 MM DRT</t>
+  </si>
+  <si>
+    <t>29512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  ADSON  150 X 1 MM   A  GR. MICRO</t>
+  </si>
+  <si>
+    <t>30907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  STAND. DELIC. 160 MM A  GR</t>
+  </si>
+  <si>
+    <t>32705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE DBL ART. MARQUARDT  200 X  3MM CBE</t>
+  </si>
+  <si>
+    <t>35401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. KOCHER          140 MM D.AG</t>
+  </si>
+  <si>
+    <t>42101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE SELVERSTONE  150 DROIT    2X 3 MM</t>
+  </si>
+  <si>
+    <t>43602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGINE MAXILLO OBWEGESER   COURBE   7 X 175 MM</t>
+  </si>
+  <si>
+    <t>57109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGINE SEDILLOT COURBE 15 X 215 MM</t>
+  </si>
+  <si>
+    <t>K1245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. DAUBENSPECK CDEE      200 X  2.0 MM</t>
+  </si>
+  <si>
+    <t>UC4323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT METZENBAUM DELICAT 145 MM CBE</t>
+  </si>
+  <si>
+    <t>X646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. CASPAR COUDEE        220 X 3.6 MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORTHOPEDIE RACHIS CERBICAL 2</t>
+  </si>
+  <si>
+    <t>02701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANULE ASPIR. FRAZIER CDEE      125 MM  D.  2,6 MM</t>
+  </si>
+  <si>
+    <t>15606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. BRUNS DROITE    230 X  4.3 MM FIG 2</t>
+  </si>
+  <si>
+    <t>15611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. BRUNS ANGULEE   230 X  1.5 MM FIG 0000</t>
+  </si>
+  <si>
+    <t>15810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. CLOWARD CTRE CDEE     200 X  2.5 MM</t>
+  </si>
+  <si>
+    <t>23002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD SS VLV 250 MM CERV</t>
+  </si>
+  <si>
+    <t>23104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD 1 VLV SEULE GR. 45 MM</t>
+  </si>
+  <si>
+    <t>23201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.RACH. CLOWARD CERV. 20 X  150 MM</t>
+  </si>
+  <si>
+    <t>24603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELEVATEUR LANGENBECK TRCH. LARG. 190 X 15 MM </t>
+  </si>
+  <si>
+    <t>30930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  STAND. NORMA. 180 MM 1 X 2 GR</t>
+  </si>
+  <si>
+    <t>41912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE FERRIS        180 DROIT   6X12</t>
+  </si>
+  <si>
+    <t>41918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR DISQUE GRUNWALD  180 DROIT   3X10 DEMONTABLE</t>
+  </si>
+  <si>
+    <t>K1244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. DAUBENSPECK CDEE      200 X  4.0 MM</t>
+  </si>
+  <si>
+    <t>K633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. LAMBOTTE           10 X 240 MM LAME FINE</t>
+  </si>
+  <si>
+    <t>K742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. DAUBENSPECK CDEE      200 X  2.8 MM</t>
+  </si>
+  <si>
+    <t>W784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE SIMPLE STELLBRINK 170X 2 MM CBE</t>
   </si>
 </sst>
 </file>
@@ -11806,7 +12158,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="74.8515625"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -11830,10 +12182,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>624</v>
+        <v>76</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>625</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -11841,10 +12193,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>405</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -11852,10 +12204,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>4</v>
+        <v>436</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>5</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7">
@@ -11863,10 +12215,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>436</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>7</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8">
@@ -11874,10 +12226,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>626</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -11885,10 +12237,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>628</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>629</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -11896,10 +12248,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11">
@@ -11907,10 +12259,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
     </row>
     <row r="12">
@@ -11918,10 +12270,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>634</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>635</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -11929,10 +12281,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>636</v>
+        <v>137</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>637</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -11940,10 +12292,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>638</v>
+        <v>271</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>639</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15">
@@ -11951,10 +12303,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>10</v>
+        <v>272</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>11</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16">
@@ -11962,10 +12314,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>10</v>
+        <v>626</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>11</v>
+        <v>627</v>
       </c>
     </row>
     <row r="17">
@@ -11973,10 +12325,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>640</v>
+        <v>599</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>641</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -11984,10 +12336,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>642</v>
+        <v>298</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>643</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19">
@@ -11995,10 +12347,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>644</v>
+        <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>232</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -12006,10 +12358,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>406</v>
+        <v>14</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>232</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -12017,10 +12369,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>645</v>
+        <v>14</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>646</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -12028,10 +12380,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>647</v>
+        <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>648</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -12039,10 +12391,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>649</v>
+        <v>14</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>650</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -12050,10 +12402,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>651</v>
+        <v>143</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>652</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
@@ -12061,10 +12413,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>653</v>
+        <v>628</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>654</v>
+        <v>629</v>
       </c>
     </row>
     <row r="26">
@@ -12072,10 +12424,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
@@ -12083,10 +12435,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>14</v>
+        <v>295</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28">
@@ -12094,10 +12446,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -12105,10 +12457,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -12116,10 +12468,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>14</v>
+        <v>630</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>15</v>
+        <v>631</v>
       </c>
     </row>
     <row r="31">
@@ -12127,10 +12479,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>655</v>
+        <v>632</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>656</v>
+        <v>633</v>
       </c>
     </row>
     <row r="32">
@@ -12138,10 +12490,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>301</v>
+        <v>464</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>302</v>
+        <v>465</v>
       </c>
     </row>
     <row r="33">
@@ -12149,10 +12501,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34">
@@ -12160,10 +12512,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>219</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35">
@@ -12171,10 +12523,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>657</v>
+        <v>147</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>658</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36">
@@ -12182,10 +12534,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>659</v>
+        <v>22</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>660</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -12193,10 +12545,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>661</v>
+        <v>24</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>662</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
@@ -12204,10 +12556,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>23</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39">
@@ -12215,10 +12567,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
@@ -12226,10 +12578,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>663</v>
+        <v>26</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>664</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -12237,10 +12589,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>665</v>
+        <v>222</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>666</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42">
@@ -12248,10 +12600,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>667</v>
+        <v>330</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>668</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43">
@@ -12259,10 +12611,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>669</v>
+        <v>34</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>670</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -12270,10 +12622,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>671</v>
+        <v>634</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>672</v>
+        <v>635</v>
       </c>
     </row>
     <row r="45">
@@ -12281,10 +12633,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>671</v>
+        <v>114</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>672</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46">
@@ -12292,10 +12644,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>673</v>
+        <v>250</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>674</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47">
@@ -12303,10 +12655,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>675</v>
+        <v>636</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>676</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48">
@@ -12314,10 +12666,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>677</v>
+        <v>336</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>678</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49">
@@ -12325,10 +12677,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>679</v>
+        <v>40</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>680</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
@@ -12336,10 +12688,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>681</v>
+        <v>71</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>232</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51">
@@ -12347,10 +12699,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>682</v>
+        <v>341</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>683</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52">
@@ -12358,10 +12710,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>684</v>
+        <v>44</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>685</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -12369,252 +12721,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>686</v>
+        <v>474</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3">
-        <v>51</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3">
-        <v>52</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3">
-        <v>53</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3">
-        <v>54</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3">
-        <v>55</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3">
-        <v>56</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3">
-        <v>57</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3">
-        <v>58</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3">
-        <v>59</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3">
-        <v>60</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3">
-        <v>61</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3">
-        <v>62</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3">
-        <v>63</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3">
-        <v>64</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3">
-        <v>65</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3">
-        <v>66</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3">
-        <v>67</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3">
-        <v>68</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3">
-        <v>69</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3">
-        <v>70</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3">
-        <v>71</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3">
-        <v>72</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>713</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -13024,7 +13134,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>714</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3">
@@ -13043,10 +13153,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -13054,10 +13164,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -13065,10 +13175,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>436</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>437</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -13076,10 +13186,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>436</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>437</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -13087,10 +13197,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -13098,10 +13208,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>242</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>11</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -13109,10 +13219,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>715</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>716</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -13120,10 +13230,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>715</v>
+        <v>147</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>716</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
@@ -13131,10 +13241,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -13142,10 +13252,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14">
@@ -13153,10 +13263,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>271</v>
+        <v>149</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -13164,10 +13274,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>272</v>
+        <v>174</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>273</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -13175,10 +13285,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>717</v>
+        <v>330</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>718</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17">
@@ -13186,10 +13296,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>599</v>
+        <v>30</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>600</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -13197,10 +13307,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>298</v>
+        <v>32</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>299</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -13208,10 +13318,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
@@ -13219,10 +13329,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21">
@@ -13230,10 +13340,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>14</v>
+        <v>638</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>15</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22">
@@ -13241,10 +13351,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>14</v>
+        <v>640</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>15</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23">
@@ -13252,10 +13362,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>14</v>
+        <v>640</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>15</v>
+        <v>641</v>
       </c>
     </row>
     <row r="24">
@@ -13263,10 +13373,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>143</v>
+        <v>353</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>144</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25">
@@ -13274,10 +13384,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>719</v>
+        <v>642</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>720</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26">
@@ -13285,10 +13395,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>51</v>
+        <v>159</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27">
@@ -13296,10 +13406,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>295</v>
+        <v>40</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
@@ -13307,10 +13417,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29">
@@ -13318,10 +13428,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -13329,263 +13439,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>661</v>
+        <v>44</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3">
-        <v>28</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3">
-        <v>29</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3">
-        <v>30</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3">
-        <v>31</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3">
-        <v>32</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3">
-        <v>33</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3">
-        <v>34</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3">
-        <v>35</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3">
-        <v>37</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3">
-        <v>38</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3">
-        <v>39</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3">
-        <v>40</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3">
-        <v>41</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3">
-        <v>42</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3">
-        <v>43</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3">
-        <v>44</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3">
         <v>45</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3">
-        <v>46</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3">
-        <v>47</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3">
-        <v>48</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3">
-        <v>49</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3">
-        <v>50</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -13614,7 +13471,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3">
@@ -13710,10 +13567,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -13820,10 +13677,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>727</v>
+        <v>638</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>728</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22">
@@ -13831,10 +13688,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>729</v>
+        <v>640</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>730</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23">
@@ -13842,10 +13699,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>729</v>
+        <v>640</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>730</v>
+        <v>641</v>
       </c>
     </row>
     <row r="24">
@@ -13864,10 +13721,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>731</v>
+        <v>642</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>732</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26">
@@ -13897,10 +13754,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>163</v>
+        <v>645</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>164</v>
+        <v>646</v>
       </c>
     </row>
     <row r="29">
@@ -13908,10 +13765,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30">
@@ -13919,9 +13776,20 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>45</v>
       </c>
     </row>
@@ -13951,7 +13819,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>733</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3">
@@ -13970,10 +13838,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -13981,10 +13849,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6">
@@ -14025,10 +13893,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>242</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>243</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -14036,10 +13904,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -14047,10 +13915,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -14058,10 +13926,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -14069,10 +13937,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>149</v>
+        <v>648</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -14080,10 +13948,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>149</v>
+        <v>649</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15">
@@ -14091,10 +13959,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>174</v>
+        <v>650</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>175</v>
+        <v>651</v>
       </c>
     </row>
     <row r="16">
@@ -14102,10 +13970,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>330</v>
+        <v>652</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>331</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17">
@@ -14113,10 +13981,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>653</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>31</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18">
@@ -14124,10 +13992,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>32</v>
+        <v>653</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>33</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19">
@@ -14135,142 +14003,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>108</v>
+        <v>654</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3">
-        <v>21</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3">
-        <v>23</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3">
-        <v>24</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3">
-        <v>25</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3">
-        <v>26</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3">
-        <v>27</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3">
-        <v>28</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>45</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -14299,7 +14035,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>736</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3">
@@ -14329,10 +14065,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>229</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>230</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -14384,10 +14120,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -14406,10 +14142,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>648</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>19</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
@@ -14417,7 +14153,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>737</v>
+        <v>649</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>232</v>
@@ -14428,7 +14164,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>738</v>
+        <v>649</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>232</v>
@@ -14439,10 +14175,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>663</v>
+        <v>30</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>664</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -14450,7 +14186,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>739</v>
+        <v>652</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>232</v>
@@ -14461,7 +14197,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>740</v>
+        <v>656</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>232</v>
@@ -14472,7 +14208,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>740</v>
+        <v>657</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>232</v>
@@ -14483,10 +14219,32 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>741</v>
+        <v>654</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>232</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -14515,7 +14273,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>742</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3">
@@ -14534,10 +14292,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
@@ -14545,10 +14303,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -14556,10 +14314,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
@@ -14567,10 +14325,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
@@ -14578,10 +14336,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>509</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">
@@ -14589,10 +14347,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -14600,131 +14358,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -14753,7 +14390,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>745</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3">
@@ -14772,10 +14409,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>240</v>
+        <v>660</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>241</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5">
@@ -14783,10 +14420,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>662</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>99</v>
+        <v>663</v>
       </c>
     </row>
     <row r="6">
@@ -14794,10 +14431,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>98</v>
+        <v>662</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>99</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7">
@@ -14805,10 +14442,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>603</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>101</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -14816,10 +14453,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>509</v>
+        <v>664</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>510</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9">
@@ -14827,10 +14464,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>666</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>68</v>
+        <v>667</v>
       </c>
     </row>
     <row r="10">
@@ -14838,10 +14475,109 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>666</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>35</v>
+        <v>667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -14861,16 +14597,16 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="60"/>
+    <col customWidth="1" min="3" max="3" width="65.00390625"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>746</v>
+        <v>681</v>
       </c>
     </row>
     <row r="3">
@@ -14889,10 +14625,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>747</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>748</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -14900,10 +14636,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>749</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>750</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -14911,10 +14647,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>749</v>
+        <v>78</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>750</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -14922,10 +14658,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -14933,10 +14669,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>751</v>
+        <v>624</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>752</v>
+        <v>625</v>
       </c>
     </row>
     <row r="9">
@@ -14944,10 +14680,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>753</v>
+        <v>80</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>754</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -14955,10 +14691,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>753</v>
+        <v>272</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>754</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -14966,10 +14702,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>755</v>
+        <v>272</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>756</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12">
@@ -14977,10 +14713,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>757</v>
+        <v>682</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>758</v>
+        <v>683</v>
       </c>
     </row>
     <row r="13">
@@ -14988,10 +14724,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>759</v>
+        <v>14</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>760</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -14999,10 +14735,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>761</v>
+        <v>14</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>762</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -15010,10 +14746,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>763</v>
+        <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -15021,10 +14757,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>765</v>
+        <v>14</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>766</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -15032,7 +14768,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>767</v>
+        <v>684</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>232</v>
@@ -15043,10 +14779,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>767</v>
+        <v>601</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>232</v>
+        <v>602</v>
       </c>
     </row>
     <row r="19">
@@ -15054,10 +14790,241 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>767</v>
+        <v>51</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -15075,18 +15042,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="67.28125"/>
+    <col customWidth="1" min="3" max="3" width="75.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>768</v>
+        <v>696</v>
       </c>
     </row>
     <row r="3">
@@ -15105,10 +15072,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>697</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>698</v>
       </c>
     </row>
     <row r="5">
@@ -15116,10 +15083,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>74</v>
+        <v>404</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>75</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6">
@@ -15127,10 +15094,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -15138,10 +15105,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>715</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>716</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -15149,10 +15116,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>716</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9">
@@ -15160,10 +15127,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>701</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>81</v>
+        <v>702</v>
       </c>
     </row>
     <row r="10">
@@ -15171,10 +15138,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>272</v>
+        <v>703</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>273</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11">
@@ -15182,10 +15149,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>272</v>
+        <v>705</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>273</v>
+        <v>706</v>
       </c>
     </row>
     <row r="12">
@@ -15193,10 +15160,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>769</v>
+        <v>707</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>770</v>
+        <v>708</v>
       </c>
     </row>
     <row r="13">
@@ -15204,10 +15171,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>709</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>15</v>
+        <v>710</v>
       </c>
     </row>
     <row r="14">
@@ -15215,10 +15182,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>711</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>15</v>
+        <v>712</v>
       </c>
     </row>
     <row r="15">
@@ -15226,10 +15193,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -15237,10 +15204,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -15248,10 +15215,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>771</v>
+        <v>713</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>232</v>
+        <v>714</v>
       </c>
     </row>
     <row r="18">
@@ -15259,10 +15226,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>601</v>
+        <v>715</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>602</v>
+        <v>716</v>
       </c>
     </row>
     <row r="19">
@@ -15270,10 +15237,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>717</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>52</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20">
@@ -15281,10 +15248,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>406</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>52</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
@@ -15292,10 +15259,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>295</v>
+        <v>718</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>296</v>
+        <v>719</v>
       </c>
     </row>
     <row r="22">
@@ -15303,10 +15270,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>603</v>
+        <v>720</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>604</v>
+        <v>721</v>
       </c>
     </row>
     <row r="23">
@@ -15314,10 +15281,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>751</v>
+        <v>722</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>752</v>
+        <v>723</v>
       </c>
     </row>
     <row r="24">
@@ -15325,10 +15292,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>772</v>
+        <v>724</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>773</v>
+        <v>725</v>
       </c>
     </row>
     <row r="25">
@@ -15336,10 +15303,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>147</v>
+        <v>726</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>148</v>
+        <v>727</v>
       </c>
     </row>
     <row r="26">
@@ -15347,10 +15314,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -15358,10 +15325,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -15369,10 +15336,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -15380,10 +15347,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -15391,10 +15358,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>222</v>
+        <v>14</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>223</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -15402,10 +15369,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>174</v>
+        <v>728</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>175</v>
+        <v>729</v>
       </c>
     </row>
     <row r="32">
@@ -15413,10 +15380,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>246</v>
+        <v>301</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>247</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33">
@@ -15424,10 +15391,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>774</v>
+        <v>53</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>775</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34">
@@ -15435,10 +15402,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>776</v>
+        <v>218</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35">
@@ -15446,10 +15413,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>777</v>
+        <v>730</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>778</v>
+        <v>731</v>
       </c>
     </row>
     <row r="36">
@@ -15457,10 +15424,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>779</v>
+        <v>732</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>780</v>
+        <v>733</v>
       </c>
     </row>
     <row r="37">
@@ -15468,10 +15435,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>167</v>
+        <v>630</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>168</v>
+        <v>631</v>
       </c>
     </row>
     <row r="38">
@@ -15479,10 +15446,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
@@ -15490,10 +15457,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>708</v>
+        <v>30</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>709</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
@@ -15501,10 +15468,395 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>708</v>
+        <v>650</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>709</v>
+        <v>651</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3">
+        <v>63</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3">
+        <v>64</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3">
+        <v>65</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3">
+        <v>66</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3">
+        <v>67</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3">
+        <v>68</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3">
+        <v>69</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3">
+        <v>70</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3">
+        <v>71</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3">
+        <v>72</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -15513,7 +15865,1451 @@
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="90" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="76.57421875"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="89" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="76.57421875"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="89" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -15906,6 +17702,1439 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="62.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3">
+        <v>63</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3">
+        <v>64</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3">
+        <v>65</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>865</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="72.421875"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>865</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="93" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="43" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,6 +49,8 @@
     <sheet name="ORTHOPEDIE RACHIS LOMBAIRE 2 (TEST)" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="ORTHOPEDIE RACHIS CERBICAL 1" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="ORTHOPEDIE RACHIS CERBICAL 2" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="VASCULAIRE 1" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="HEPATOBILIAIRE 1" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="992">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -2752,6 +2754,288 @@
   </si>
   <si>
     <t xml:space="preserve">PINCE GOUGE SIMPLE STELLBRINK 170X 2 MM CBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VASCULAIRE 1</t>
+  </si>
+  <si>
+    <t>02805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANULE HEPARINE  D. 2.5 MM EMB.4 MM FIG 1</t>
+  </si>
+  <si>
+    <t>08618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG          FORT 60 MM  COURBE</t>
+  </si>
+  <si>
+    <t>08620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG          FORT 70 MM  COURBE</t>
+  </si>
+  <si>
+    <t>08701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG DEBAKEY       DRT      80  X 20 MM</t>
+  </si>
+  <si>
+    <t>08702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG DEBAKEY       DRT      90  X 30 MM</t>
+  </si>
+  <si>
+    <t>08703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG DEBAKEY       DRT    105  X 45 MM</t>
+  </si>
+  <si>
+    <t>08704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG DEBAKEY       DRT    125  X 68 MM</t>
+  </si>
+  <si>
+    <t>08705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG DEBAKEY       CRBE    75  X 20 MM</t>
+  </si>
+  <si>
+    <t>08706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG DEBAKEY       CRBE    85  X 30 MM</t>
+  </si>
+  <si>
+    <t>08707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG DEBAKEY       CRBE    95  X 45 MM</t>
+  </si>
+  <si>
+    <t>08708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG DEBAKEY       CRBE  115  X 68 MM</t>
+  </si>
+  <si>
+    <t>08717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG ATRAU. CAROT. DEBAKEY SATINSKY CONTRE COUDE 90MM</t>
+  </si>
+  <si>
+    <t>08718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG ATRAU. DEBAKEY SATINSKY CONTRE COUDE 70MM</t>
+  </si>
+  <si>
+    <t>08906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG JOHN HOPKINS COURBE 90MM</t>
+  </si>
+  <si>
+    <t>13908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROCHET CRILE                220 MM MSSE 90°</t>
+  </si>
+  <si>
+    <t>18205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE CUSHING         16 MM  200 MM</t>
+  </si>
+  <si>
+    <t>21908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.BECKMANN      MSS    20X 300 MM</t>
+  </si>
+  <si>
+    <t>22004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.BECKMANN CONE MSS     20X 330 MM</t>
+  </si>
+  <si>
+    <t>22807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.WEITLANER GR. MSS 3 X 4  200 MM</t>
+  </si>
+  <si>
+    <t>29903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  DEBAKEY 1.5   240 MM DRT ATRAUMA</t>
+  </si>
+  <si>
+    <t>30305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  GERALD       180 X 1,5 MM SS GR.</t>
+  </si>
+  <si>
+    <t>30703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  POTTS SMITH   200 MM A  GR</t>
+  </si>
+  <si>
+    <t>30707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  POTTS SMITH   200 MM TUNGST</t>
+  </si>
+  <si>
+    <t>34204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. BENGOLEA        210 MM D.SG</t>
+  </si>
+  <si>
+    <t>34904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. HALSTEAD         100 MM D.SG</t>
+  </si>
+  <si>
+    <t>43901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGINE SEMB COSTALE     FIG. 1    12 X 195 MM</t>
+  </si>
+  <si>
+    <t>51144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. LURZ  URETERALE 210 MM</t>
+  </si>
+  <si>
+    <t>51714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG ATRAU. DEBAKEY SATINSKY  100MM</t>
+  </si>
+  <si>
+    <t>55935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. HARTMANN 100MM CBE SS GR</t>
+  </si>
+  <si>
+    <t>UC4326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT METZENBAUM DELICAT 230 MM CBE</t>
+  </si>
+  <si>
+    <t>UC4366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT POTTS SMITH        190 MM  25°</t>
+  </si>
+  <si>
+    <t>UC4367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT POTTS SMITH        190 MM  45°</t>
+  </si>
+  <si>
+    <t>UC4371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT ALLAINES   180 MM CBE -S- FORM</t>
+  </si>
+  <si>
+    <t>UC4410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT DIETRICH   190 MM  90° LAME MICRO</t>
+  </si>
+  <si>
+    <t>UC4411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT DIETRICH   190 MM 125° LAME MICRO</t>
+  </si>
+  <si>
+    <t>UN010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UP-NEEDLE DEBAKEY                     180 MM       4/0 A 6/0</t>
+  </si>
+  <si>
+    <t>UN020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UP-NEEDLE DEBAKEY                     230 MM       4/0 A 6/0</t>
+  </si>
+  <si>
+    <t>UN466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UP-NEEDLE RYDER MICRO            150 MM       6/0 A 8/0</t>
+  </si>
+  <si>
+    <t>UN468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UP-NEEDLE RYDER MICRO            200 MM       6/0 A 8/0</t>
+  </si>
+  <si>
+    <t>UN469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UP-NEEDLE RYDER MICRO            230 MM       6/0 A 8/0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEPATOBILIAIRE 1</t>
+  </si>
+  <si>
+    <t>17510</t>
+  </si>
+  <si>
+    <t>25610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAME MALLEABLE LARDENNOIS 30 X 50 X 360 MM</t>
+  </si>
+  <si>
+    <t>55952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSE FILS GEMINI 250 MM</t>
+  </si>
+  <si>
+    <t>55967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSE FILS GEMINI 230MM</t>
+  </si>
+  <si>
+    <t>56614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. ROBERTS       220 MM C.SG</t>
+  </si>
+  <si>
+    <t>UL130</t>
+  </si>
+  <si>
+    <t>UL34306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. BENGOLEA SUED.  240 MM C.SG UPLINE</t>
   </si>
 </sst>
 </file>
@@ -18643,14 +18927,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>867</v>
       </c>
@@ -19302,6 +19586,1714 @@
       </c>
       <c r="C61" s="4" t="s">
         <v>866</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="69.00390625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3">
+        <v>63</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3">
+        <v>64</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3">
+        <v>65</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3">
+        <v>66</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3">
+        <v>67</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3">
+        <v>68</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3">
+        <v>69</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3">
+        <v>70</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3">
+        <v>71</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3">
+        <v>72</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3">
+        <v>73</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3">
+        <v>74</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3">
+        <v>75</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3">
+        <v>76</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3">
+        <v>77</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3">
+        <v>78</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3">
+        <v>79</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3">
+        <v>80</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3">
+        <v>81</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3">
+        <v>82</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3">
+        <v>83</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3">
+        <v>85</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3">
+        <v>86</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3">
+        <v>87</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3">
+        <v>88</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3">
+        <v>89</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3">
+        <v>90</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3">
+        <v>91</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3">
+        <v>92</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3">
+        <v>93</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>978</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="61.8515625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -19321,14 +21313,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="61.140625"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="43" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="44" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -51,6 +51,7 @@
     <sheet name="ORTHOPEDIE RACHIS CERBICAL 2" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="VASCULAIRE 1" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="HEPATOBILIAIRE 1" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="GOITRE 3" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="1005">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -3036,6 +3037,45 @@
   </si>
   <si>
     <t xml:space="preserve">PINCE HEM. BENGOLEA SUED.  240 MM C.SG UPLINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOITRE 3</t>
+  </si>
+  <si>
+    <t>29901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  DEBAKEY 1.5   160 MM DRT ATRAUMA</t>
+  </si>
+  <si>
+    <t>34911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. HALSTEAD         120 MM MICRO D.AG</t>
+  </si>
+  <si>
+    <t>35511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. LERICHE         150 MM C.AG</t>
+  </si>
+  <si>
+    <t>38603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE PREHENS. AJOURE DUVAL 200 X 13 MM TUNGST</t>
+  </si>
+  <si>
+    <t>UL35008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. HALSTEAD MICRO   120 MM D.SG UPLINE</t>
+  </si>
+  <si>
+    <t>UL35606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. LERICHE         150 MM D.AG UPLINE</t>
   </si>
 </sst>
 </file>
@@ -19605,14 +19645,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="69.00390625"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>898</v>
       </c>
@@ -20672,7 +20712,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="61.8515625"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -21294,6 +21334,563 @@
       </c>
       <c r="C58" s="4" t="s">
         <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="63.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="45" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="43" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -50,9 +50,14 @@
     <sheet name="ORTHOPEDIE RACHIS LOMBAIRE 2 (TEST)" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="ORTHOPEDIE RACHIS CERBICAL 1" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="ORTHOPEDIE RACHIS CERBICAL 2" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="VASCULAIRE 1" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="HEPATOBILIAIRE 1" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="GOITRE 3" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="ORTHOPEDIE HANCHE 1" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="ORTHOPEDIE HANCHE 2" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="VASCULAIRE 1" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="HEPATOBILIAIRE 1" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="GOITRE 3" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="CURETTAGE 2" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="CURETTAGE 3" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="CURETTAGE 4" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -62,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="1068">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -2761,6 +2766,195 @@
     <t xml:space="preserve">PINCE GOUGE SIMPLE STELLBRINK 170X 2 MM CBE</t>
   </si>
   <si>
+    <t xml:space="preserve">ORTHOPEDIE HANCHE 1</t>
+  </si>
+  <si>
+    <t>08209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. STILLE DROIT       15 X 210 MM</t>
+  </si>
+  <si>
+    <t>08216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. STILLE COURBE   20 X 210 MM</t>
+  </si>
+  <si>
+    <t>11208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE A DISS. LIGATURE  ZENKER COURBE 290MM</t>
+  </si>
+  <si>
+    <t>14303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROCHET LAMBOTTE         280 MM GRAND MODELE</t>
+  </si>
+  <si>
+    <t>15618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. BRUNS ANGULEE   230 X  6.1 MM FIG 4</t>
+  </si>
+  <si>
+    <t>15856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. VOLKMANN              280 X 10 MM</t>
+  </si>
+  <si>
+    <t>18004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE BENNET        65 MM    260 MM</t>
+  </si>
+  <si>
+    <t>18703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE HOHMANN 265 MM  24.0 MM</t>
+  </si>
+  <si>
+    <t>19605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR /MANCHE SIMON 27 X 115 MM</t>
+  </si>
+  <si>
+    <t>22004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR AUT.BECKMANN CONE MSS     20X 330 MM</t>
+  </si>
+  <si>
+    <t>24602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELEVATEUR LAMBOTTE CUILLER DOUBLE  290 MM LARGEUR 15 ET 30MM</t>
+  </si>
+  <si>
+    <t>25812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MASSE OMBREDANNE 230MM DIAM 40 MM 900 GR</t>
+  </si>
+  <si>
+    <t>26709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSE FILS OSHAUGN.FIN  220 MM CDE 45°</t>
+  </si>
+  <si>
+    <t>29004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE COUPANTE DBL ART. LISTON 270 MM DROITE</t>
+  </si>
+  <si>
+    <t>30936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  STAND. NORMA. 250 MM 1 X 2 GR</t>
+  </si>
+  <si>
+    <t>32803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE DBL ART. RUSKIN     240 X  5MM CBE</t>
+  </si>
+  <si>
+    <t>34003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GYNECO WERTHEIM CBE A  GR            230 MM</t>
+  </si>
+  <si>
+    <t>43308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGINE LAMBOTTE                   20 X 210 MM</t>
+  </si>
+  <si>
+    <t>56614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE HEM. ROBERTS       220 MM C.SG</t>
+  </si>
+  <si>
+    <t>A6QK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POINTE CARREE PERTHES                  210 MM (alene)</t>
+  </si>
+  <si>
+    <t>CAXC</t>
+  </si>
+  <si>
+    <t>K536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS GOUGE  MANCHE SYNTH.   5 X 250 MM</t>
+  </si>
+  <si>
+    <t>Z593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAVIER OS VERBRUGGE REDUCT. AUTO CENTR.  260 MM</t>
+  </si>
+  <si>
+    <t>Z594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAVIER OS VERBRUGGE REDUCT. AUTO CENTR.  280 MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORTHOPEDIE HANCHE 2</t>
+  </si>
+  <si>
+    <t>04121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX DISS. METZ.NELSON 250 MM CBE  TUNGST</t>
+  </si>
+  <si>
+    <t>08114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. LAMBOTTE           14 X 240 MM</t>
+  </si>
+  <si>
+    <t>08210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. STILLE DROIT       20 X 210 MM</t>
+  </si>
+  <si>
+    <t>08213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. STILLE COURBE   10 X 210 MM</t>
+  </si>
+  <si>
+    <t>15855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. VOLKMANN              280 X   8 MM</t>
+  </si>
+  <si>
+    <t>30913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE DISS.  STAND. DELIC. 250 MM A  GR</t>
+  </si>
+  <si>
+    <t>32602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE GOUGE DBL ART. LEKSELL    230 X  5MM</t>
+  </si>
+  <si>
     <t xml:space="preserve">VASCULAIRE 1</t>
   </si>
   <si>
@@ -2866,12 +3060,6 @@
     <t xml:space="preserve">ECARTEUR AUT.BECKMANN      MSS    20X 300 MM</t>
   </si>
   <si>
-    <t>22004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECARTEUR AUT.BECKMANN CONE MSS     20X 330 MM</t>
-  </si>
-  <si>
     <t>22807</t>
   </si>
   <si>
@@ -3028,12 +3216,6 @@
     <t xml:space="preserve">PASSE FILS GEMINI 230MM</t>
   </si>
   <si>
-    <t>56614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINCE HEM. ROBERTS       220 MM C.SG</t>
-  </si>
-  <si>
     <t>UL130</t>
   </si>
   <si>
@@ -3080,6 +3262,15 @@
   </si>
   <si>
     <t xml:space="preserve">PINCE HEM. LERICHE         150 MM D.AG UPLINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTAGE 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTAGE 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTAGE 4</t>
   </si>
 </sst>
 </file>
@@ -19909,14 +20100,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="60"/>
+    <col customWidth="1" min="3" max="3" width="68.8515625"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>899</v>
       </c>
@@ -19948,10 +20139,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -19970,10 +20161,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -19981,10 +20172,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>900</v>
+        <v>81</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>901</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -19992,10 +20183,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>365</v>
+        <v>900</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>366</v>
+        <v>901</v>
       </c>
     </row>
     <row r="10">
@@ -20058,10 +20249,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>912</v>
+        <v>273</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>913</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16">
@@ -20069,10 +20260,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>914</v>
+        <v>273</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>915</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17">
@@ -20080,10 +20271,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
     </row>
     <row r="18">
@@ -20091,10 +20282,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>918</v>
+        <v>585</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>919</v>
+        <v>586</v>
       </c>
     </row>
     <row r="19">
@@ -20102,10 +20293,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>920</v>
+        <v>585</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>921</v>
+        <v>586</v>
       </c>
     </row>
     <row r="20">
@@ -20113,10 +20304,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>922</v>
+        <v>587</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>923</v>
+        <v>588</v>
       </c>
     </row>
     <row r="21">
@@ -20124,10 +20315,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>924</v>
+        <v>589</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>925</v>
+        <v>590</v>
       </c>
     </row>
     <row r="22">
@@ -20135,10 +20326,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
     </row>
     <row r="23">
@@ -20146,10 +20337,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
     </row>
     <row r="24">
@@ -20157,10 +20348,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>928</v>
+        <v>918</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>929</v>
+        <v>919</v>
       </c>
     </row>
     <row r="25">
@@ -20168,10 +20359,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>930</v>
+        <v>724</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>931</v>
+        <v>725</v>
       </c>
     </row>
     <row r="26">
@@ -20179,10 +20370,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
     </row>
     <row r="27">
@@ -20190,10 +20381,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>932</v>
+        <v>922</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>933</v>
+        <v>923</v>
       </c>
     </row>
     <row r="28">
@@ -20201,10 +20392,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>722</v>
+        <v>924</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>723</v>
+        <v>925</v>
       </c>
     </row>
     <row r="29">
@@ -20212,10 +20403,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>595</v>
+        <v>14</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>596</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -20223,10 +20414,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>934</v>
+        <v>14</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>935</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -20234,10 +20425,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>934</v>
+        <v>14</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>935</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -20245,10 +20436,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>936</v>
+        <v>14</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>937</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -20256,10 +20447,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>299</v>
+        <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>300</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -20267,10 +20458,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>408</v>
+        <v>926</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>409</v>
+        <v>927</v>
       </c>
     </row>
     <row r="35">
@@ -20278,10 +20469,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>14</v>
+        <v>410</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>15</v>
+        <v>411</v>
       </c>
     </row>
     <row r="36">
@@ -20289,10 +20480,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37">
@@ -20300,10 +20491,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -20311,10 +20502,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>14</v>
+        <v>928</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>15</v>
+        <v>929</v>
       </c>
     </row>
     <row r="39">
@@ -20322,10 +20513,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>14</v>
+        <v>666</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>15</v>
+        <v>667</v>
       </c>
     </row>
     <row r="40">
@@ -20333,10 +20524,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>14</v>
+        <v>930</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>15</v>
+        <v>931</v>
       </c>
     </row>
     <row r="41">
@@ -20344,10 +20535,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>938</v>
+        <v>97</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>939</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42">
@@ -20355,10 +20546,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>938</v>
+        <v>97</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>939</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43">
@@ -20366,10 +20557,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>410</v>
+        <v>932</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>411</v>
+        <v>933</v>
       </c>
     </row>
     <row r="44">
@@ -20377,10 +20568,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>410</v>
+        <v>103</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>411</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45">
@@ -20388,10 +20579,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>940</v>
+        <v>103</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>941</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46">
@@ -20399,10 +20590,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>942</v>
+        <v>22</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>943</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
@@ -20410,10 +20601,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>944</v>
+        <v>22</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>945</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
@@ -20421,10 +20612,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>944</v>
+        <v>225</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>945</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49">
@@ -20432,10 +20623,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50">
@@ -20443,10 +20634,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>53</v>
+        <v>934</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>54</v>
+        <v>935</v>
       </c>
     </row>
     <row r="51">
@@ -20454,10 +20645,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>18</v>
+        <v>936</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>19</v>
+        <v>937</v>
       </c>
     </row>
     <row r="52">
@@ -20465,10 +20656,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>55</v>
+        <v>938</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>56</v>
+        <v>939</v>
       </c>
     </row>
     <row r="53">
@@ -20476,10 +20667,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>55</v>
+        <v>940</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>56</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54">
@@ -20487,10 +20678,10 @@
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>55</v>
+        <v>162</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>56</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55">
@@ -20498,10 +20689,10 @@
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56">
@@ -20509,10 +20700,10 @@
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
     </row>
     <row r="57">
@@ -20520,10 +20711,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>946</v>
+        <v>129</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>947</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58">
@@ -20531,10 +20722,10 @@
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>946</v>
+        <v>44</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>947</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
@@ -20542,10 +20733,10 @@
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
@@ -20553,10 +20744,10 @@
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>103</v>
+        <v>696</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>104</v>
+        <v>697</v>
       </c>
     </row>
     <row r="61">
@@ -20564,10 +20755,10 @@
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>948</v>
+        <v>696</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>949</v>
+        <v>697</v>
       </c>
     </row>
     <row r="62">
@@ -20575,10 +20766,10 @@
         <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>948</v>
+        <v>619</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>949</v>
+        <v>620</v>
       </c>
     </row>
     <row r="63">
@@ -20586,10 +20777,10 @@
         <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="64">
@@ -20597,362 +20788,10 @@
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3">
-        <v>62</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3">
-        <v>63</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3">
-        <v>64</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3">
-        <v>65</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3">
-        <v>66</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3">
-        <v>67</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3">
-        <v>68</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3">
-        <v>69</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3">
-        <v>70</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>950</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3">
-        <v>71</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>952</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3">
-        <v>72</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>954</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3">
-        <v>73</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>956</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3">
-        <v>74</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3">
-        <v>75</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3">
-        <v>76</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3">
-        <v>77</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3">
-        <v>78</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3">
-        <v>79</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>958</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3">
-        <v>80</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>958</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3">
-        <v>81</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>960</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3">
-        <v>82</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3">
-        <v>83</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>964</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3">
-        <v>84</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3">
-        <v>85</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3">
-        <v>86</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3">
-        <v>87</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>972</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3">
-        <v>88</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>972</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3">
-        <v>89</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3">
-        <v>90</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3">
-        <v>91</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>974</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3">
-        <v>92</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>976</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3">
-        <v>93</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>978</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>979</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -20961,7 +20800,7 @@
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -20972,16 +20811,16 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="60"/>
+    <col customWidth="1" min="3" max="3" width="69.140625"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>980</v>
+        <v>947</v>
       </c>
     </row>
     <row r="3">
@@ -21000,10 +20839,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>699</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5">
@@ -21011,10 +20850,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>7</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
@@ -21022,10 +20861,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>405</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7">
@@ -21033,10 +20872,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -21044,10 +20883,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -21055,10 +20894,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>981</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>235</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -21066,10 +20905,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>235</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -21077,10 +20916,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -21088,10 +20927,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>85</v>
+        <v>948</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>949</v>
       </c>
     </row>
     <row r="13">
@@ -21099,10 +20938,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>982</v>
+        <v>950</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>983</v>
+        <v>951</v>
       </c>
     </row>
     <row r="14">
@@ -21110,10 +20949,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>952</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>15</v>
+        <v>953</v>
       </c>
     </row>
     <row r="15">
@@ -21121,10 +20960,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
+        <v>954</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>15</v>
+        <v>955</v>
       </c>
     </row>
     <row r="16">
@@ -21132,10 +20971,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>571</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>15</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17">
@@ -21143,10 +20982,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>14</v>
+        <v>956</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>15</v>
+        <v>957</v>
       </c>
     </row>
     <row r="18">
@@ -21154,10 +20993,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>14</v>
+        <v>272</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>15</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19">
@@ -21165,10 +21004,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>14</v>
+        <v>273</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>15</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20">
@@ -21176,10 +21015,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>146</v>
+        <v>912</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>147</v>
+        <v>913</v>
       </c>
     </row>
     <row r="21">
@@ -21187,10 +21026,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>410</v>
+        <v>585</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>411</v>
+        <v>586</v>
       </c>
     </row>
     <row r="22">
@@ -21198,10 +21037,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>51</v>
+        <v>585</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>52</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23">
@@ -21209,10 +21048,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>18</v>
+        <v>587</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>19</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24">
@@ -21220,10 +21059,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>412</v>
+        <v>589</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>413</v>
+        <v>590</v>
       </c>
     </row>
     <row r="25">
@@ -21231,10 +21070,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>412</v>
+        <v>916</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>413</v>
+        <v>917</v>
       </c>
     </row>
     <row r="26">
@@ -21242,10 +21081,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>55</v>
+        <v>724</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>56</v>
+        <v>725</v>
       </c>
     </row>
     <row r="27">
@@ -21253,10 +21092,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>55</v>
+        <v>724</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>56</v>
+        <v>725</v>
       </c>
     </row>
     <row r="28">
@@ -21264,10 +21103,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>22</v>
+        <v>922</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>23</v>
+        <v>923</v>
       </c>
     </row>
     <row r="29">
@@ -21275,10 +21114,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>924</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>23</v>
+        <v>925</v>
       </c>
     </row>
     <row r="30">
@@ -21286,10 +21125,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -21297,10 +21136,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -21308,10 +21147,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -21319,10 +21158,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -21330,10 +21169,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -21341,10 +21180,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>67</v>
+        <v>926</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>68</v>
+        <v>927</v>
       </c>
     </row>
     <row r="36">
@@ -21352,10 +21191,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>67</v>
+        <v>958</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>68</v>
+        <v>959</v>
       </c>
     </row>
     <row r="37">
@@ -21363,10 +21202,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>296</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>180</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38">
@@ -21374,10 +21213,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -21385,10 +21224,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40">
@@ -21396,10 +21235,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>111</v>
+        <v>960</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>112</v>
+        <v>961</v>
       </c>
     </row>
     <row r="41">
@@ -21407,10 +21246,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42">
@@ -21418,10 +21257,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>38</v>
+        <v>932</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>39</v>
+        <v>933</v>
       </c>
     </row>
     <row r="43">
@@ -21429,10 +21268,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>414</v>
+        <v>103</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>415</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
@@ -21440,10 +21279,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>984</v>
+        <v>22</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>985</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -21451,10 +21290,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>986</v>
+        <v>22</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>987</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
@@ -21462,10 +21301,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>988</v>
+        <v>225</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>989</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47">
@@ -21473,10 +21312,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>988</v>
+        <v>30</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>989</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -21484,10 +21323,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>123</v>
+        <v>934</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>124</v>
+        <v>935</v>
       </c>
     </row>
     <row r="49">
@@ -21495,10 +21334,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>40</v>
+        <v>936</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>41</v>
+        <v>937</v>
       </c>
     </row>
     <row r="50">
@@ -21506,10 +21345,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>125</v>
+        <v>938</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>126</v>
+        <v>939</v>
       </c>
     </row>
     <row r="51">
@@ -21517,10 +21356,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>166</v>
+        <v>615</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>167</v>
+        <v>616</v>
       </c>
     </row>
     <row r="52">
@@ -21528,10 +21367,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53">
@@ -21539,10 +21378,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54">
@@ -21550,10 +21389,10 @@
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>129</v>
+        <v>941</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>130</v>
+        <v>942</v>
       </c>
     </row>
     <row r="55">
@@ -21561,10 +21400,10 @@
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>990</v>
+        <v>44</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>235</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
@@ -21572,10 +21411,10 @@
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>991</v>
+        <v>46</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>992</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57">
@@ -21583,10 +21422,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>991</v>
+        <v>696</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>992</v>
+        <v>697</v>
       </c>
     </row>
     <row r="58">
@@ -21594,10 +21433,32 @@
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>46</v>
+        <v>696</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>47</v>
+        <v>697</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -21617,6 +21478,1714 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3">
+        <v>63</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3">
+        <v>64</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3">
+        <v>65</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3">
+        <v>66</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3">
+        <v>67</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3">
+        <v>68</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3">
+        <v>69</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3">
+        <v>70</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3">
+        <v>71</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3">
+        <v>72</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3">
+        <v>73</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3">
+        <v>74</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3">
+        <v>75</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3">
+        <v>76</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3">
+        <v>77</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3">
+        <v>78</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3">
+        <v>79</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3">
+        <v>80</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3">
+        <v>81</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3">
+        <v>82</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3">
+        <v>83</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3">
+        <v>85</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3">
+        <v>86</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3">
+        <v>87</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3">
+        <v>88</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3">
+        <v>89</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3">
+        <v>90</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3">
+        <v>91</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3">
+        <v>92</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3">
+        <v>93</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
@@ -21626,7 +23195,7 @@
   <sheetData>
     <row r="1" ht="21">
       <c r="A1" s="1" t="s">
-        <v>993</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="3">
@@ -21810,10 +23379,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>994</v>
+        <v>1053</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>995</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="20">
@@ -21865,10 +23434,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>996</v>
+        <v>1055</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>997</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="25">
@@ -21876,10 +23445,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>996</v>
+        <v>1055</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>997</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="26">
@@ -21898,10 +23467,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>998</v>
+        <v>1057</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>999</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="28">
@@ -21975,10 +23544,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1000</v>
+        <v>1059</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1001</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="35">
@@ -22019,10 +23588,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>956</v>
+        <v>1017</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>957</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="39">
@@ -22096,10 +23665,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1002</v>
+        <v>1061</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>1003</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="46">
@@ -22107,10 +23676,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1002</v>
+        <v>1061</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>1003</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="47">
@@ -22118,10 +23687,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1002</v>
+        <v>1061</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1003</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="48">
@@ -22129,10 +23698,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>1004</v>
+        <v>1063</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1005</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="49">
@@ -22155,6 +23724,266 @@
       </c>
       <c r="C50" s="4" t="s">
         <v>476</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -22560,6 +24389,471 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="43" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="51" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -58,6 +58,7 @@
     <sheet name="CURETTAGE 2" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="CURETTAGE 3" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="CURETTAGE 4" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="FAV 1" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="1083">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -3271,6 +3272,51 @@
   </si>
   <si>
     <t xml:space="preserve">CURETTAGE 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAV 1</t>
+  </si>
+  <si>
+    <t>08601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG             FIN  35 MM  DROIT</t>
+  </si>
+  <si>
+    <t>08602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAMP BULLDOG             FIN  35 MM  COURBE</t>
+  </si>
+  <si>
+    <t>17503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR DBL FARABEUF (PAIRE) 100 MM L.P  6X15 L.P  7X18</t>
+  </si>
+  <si>
+    <t>35006</t>
+  </si>
+  <si>
+    <t>38914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE PREHENS. MULTIGR. JUDD ALLIS  150 MM  3 X 4</t>
+  </si>
+  <si>
+    <t>39701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTE AIG. BAUMGARTNER     140 MM TUNGST</t>
+  </si>
+  <si>
+    <t>UC4341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISEAUX UP-CUT STEVENS            110 MM CBE</t>
+  </si>
+  <si>
+    <t>UL3500</t>
   </si>
 </sst>
 </file>
@@ -20104,7 +20150,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="68.8515625"/>
+    <col customWidth="1" min="3" max="3" width="69.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -20800,7 +20846,7 @@
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -20811,14 +20857,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="69.140625"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>947</v>
       </c>
@@ -23186,14 +23232,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>1052</v>
       </c>
@@ -24854,6 +24900,460 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="61.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="51" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="52" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -59,6 +59,7 @@
     <sheet name="CURETTAGE 3" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="CURETTAGE 4" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="FAV 1" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="ENDOSCOPIE HYPOPHYSE 1" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="1113">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -3317,6 +3318,96 @@
   </si>
   <si>
     <t>UL3500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDOSCOPIE HYPOPHYSE 1</t>
+  </si>
+  <si>
+    <t>08134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS. OS OSTEOT. LAMBOTTE             25 X 240 MM COURBE</t>
+  </si>
+  <si>
+    <t>37016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE ORL OTOLOGIE PANS. POLITZER 140 MR STRIE</t>
+  </si>
+  <si>
+    <t>42390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONGEUR LAMINA PUNCH PM 200 X 1 MM 40° HT   DEM. NON DETACH.</t>
+  </si>
+  <si>
+    <t>43402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGINE LEMPERT         1/2 COURBE  4 X 210 MM</t>
+  </si>
+  <si>
+    <t>50617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BISTOURI DE PLESTER DRT DIAM 3,5 X155MM</t>
+  </si>
+  <si>
+    <t>54306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAILLET WILLIGER 20X165MM 140g</t>
+  </si>
+  <si>
+    <t>56609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE ORL RHINO WEIL BLAKESLEY DROITE 3.5MM</t>
+  </si>
+  <si>
+    <t>A7ZC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE ORL RHINO LUBET BARBON LISSES     DGT 210 MM</t>
+  </si>
+  <si>
+    <t>A7ZN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE ORL RHINO LUC MRS PLEIN   A DGT PETITE</t>
+  </si>
+  <si>
+    <t>K1246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE OSS. DAUBENSPECK CDEE      200 X  5.0 MM</t>
+  </si>
+  <si>
+    <t>N933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE NEURO HARDY 260 X 4 MM MALLEABLE</t>
+  </si>
+  <si>
+    <t>N934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURETTE NEURO HARDY 260 X 6 MM MALLEABLE</t>
+  </si>
+  <si>
+    <t>U2705</t>
+  </si>
+  <si>
+    <t>UL145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UP-LIGHT S/MCH TITANE RUG.BAION.220MM CBE 2MMP</t>
+  </si>
+  <si>
+    <t>Z385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE ORL RHINO WEIL BLAKESLEY 125 X 3,5 MM CDE HT</t>
   </si>
 </sst>
 </file>
@@ -20146,14 +20237,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="69.28125"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>899</v>
       </c>
@@ -24910,7 +25001,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="61.7109375"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -25341,6 +25432,420 @@
       </c>
       <c r="C41" s="4" t="s">
         <v>1036</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="69.00390625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>1112</v>
       </c>
     </row>
   </sheetData>

--- a/public/instruments_inventory.xlsx
+++ b/public/instruments_inventory.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="52" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="53" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="CESARIENNE 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -60,6 +60,7 @@
     <sheet name="CURETTAGE 4" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="FAV 1" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="ENDOSCOPIE HYPOPHYSE 1" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="ADENOME PROSTATE (AP) 1" sheetId="54" state="visible" r:id="rId54"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="1123">
   <si>
     <t xml:space="preserve">CESARIENNE 2</t>
   </si>
@@ -3408,6 +3409,36 @@
   </si>
   <si>
     <t xml:space="preserve">PINCE ORL RHINO WEIL BLAKESLEY 125 X 3,5 MM CDE HT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADENOME PROSTATE (AP) 1</t>
+  </si>
+  <si>
+    <t>20902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR ABDOM. GOSSET AV CREM. 45 X 60 X 200</t>
+  </si>
+  <si>
+    <t>21103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECARTEUR ABDOM. JUDD MASSON COMPLET</t>
+  </si>
+  <si>
+    <t>34103</t>
+  </si>
+  <si>
+    <t>38916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINCE PREHENS. MULTIGR. THOMS ALLIS  200 MM  6 X 7</t>
+  </si>
+  <si>
+    <t>47502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVE LERICHE BUGATTI            35 X 210 MM</t>
   </si>
 </sst>
 </file>
@@ -24997,14 +25028,14 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
     <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>1068</v>
       </c>
@@ -25455,7 +25486,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8"/>
     <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="69.00390625"/>
+    <col customWidth="1" min="3" max="3" width="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="21">
@@ -25855,6 +25886,574 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="69.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.29999999999999999" right="0" top="0.29999999999999999" bottom="0" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="109" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
